--- a/data/call-qualifications.xlsx
+++ b/data/call-qualifications.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:R12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -460,10 +460,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-27T12:45:16.133Z</v>
+        <v>2026-04-28T04:27:32.498Z</v>
       </c>
       <c r="C2" t="str">
-        <v>+917567704665</v>
+        <v>+919328481970</v>
       </c>
       <c r="D2" t="str">
         <v/>
@@ -478,36 +478,271 @@
         <v>1</v>
       </c>
       <c r="H2">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="I2" t="str">
-        <v>Gujarati</v>
+        <v>Hindi</v>
       </c>
       <c r="J2" t="str">
-        <v>gu</v>
+        <v>hi</v>
       </c>
       <c r="K2" t="str">
         <v>English, Gujarati, Hindi</v>
       </c>
       <c r="L2" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M2" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="N2" t="str">
+        <v>unknown</v>
+      </c>
+      <c r="O2" t="str">
+        <v>हाँ, please आपकी टीम से जोड़ दीजिए।धन्यवाद।</v>
+      </c>
+      <c r="P2" t="str">
+        <v>CAca70fdba4d8eb7dad13e25cadb2705e3</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>conv_5701kq95b2w1etfvyrg86wd6wn8j</v>
+      </c>
+      <c r="R2" t="str" xml:space="preserve">
+        <v xml:space="preserve">Agent: Namaste 
+I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
+Would you be willing to hear a brief message about Maa Umiya and our mission?
+Umiya Dham is being developed as one of the tallest temples in the world, symbolizing strength, devotion, and cultural pride, and spreading a message of unity and spirituality.
+At Vishv Umiya Foundation, the mission is to uplift society through spirituality, education, healthcare, a...
+Prospect: હા, હિન્દી.
+Agent: धन्यवाद 🙏आप किस भाषा में सुनना पसंद करेंगे — हिंदी, अंग्रेजी, या गुजराती?क्या आप एक संक्षिप्त संदेश...
+Prospect: हिंदी में।
+Agent: धन्यवाद 🙏उमिया धाम दुनिया के सबसे ऊंचे मंदिरों में से एक के रूप में विकसित किया जा रहा है, जो आस्था, एकता और भक्ति का प्रतीक है।विश्व उमिया फाउंडेशन सामाजिक कल्याण, शिक्षा, स्वास्थ्य और आध्यात्मिक विकास के माध्यम से समाज की सेवा करता है।क्या आप अधिक जानकारी चाहेंगे या हमारी टीम से जुड़ना चाहेंगे?
+Prospect: हाँ, मैं अधिक जानकारी चाह-- अ, लेना चाहता हूँ।
+Agent: वाह बहुत अच्छा 🙏 आपको अधिक जानकारी चाहिए, तो बताता हूँ — उमिया धाम एक ऐतिहासिक और आध्यात्मिक केंद्र के रूप में विकसित किया जा रहा है, जो भारत के अहमदाबाद में स्थित है। यह न केवल एक मंदिर है, बल्कि एक विशाल सामाजिक और आध्यात्मिक केंद्र है, जो शिक्षा, स्वास्थ्य सेवाएं, ग्रामीण विकास और युवा सशक्तिकरण में लगी हुई है।आप वेबसाइट पर जाकर अधिक जानकारी प्राप्त कर सकते हैं — https://www.vuf.org/क्या आप चाहेंगे कि मैं आपको हमारी टीम से जोड़ दूं?
+Prospect: हाँ, please आपकी टीम से जोड़ दीजिए।धन्यवाद।
+Agent: वाह बहुत अच्छा 🙏 आपको हमारी टीम से जोड़ा जा रहा है।एक मिनट का इंतजार कीजिए, आपको तुरंत संपर्क किया जाएगा।धन्यवाद आपके समय के लिए।माँ उमिया आप और आपके परिवार को आशीर्वाद दे।शुभ दिन हो।जय माँ उमिया 🙏</v>
+      </c>
+    </row>
+    <row r="3" xml:space="preserve">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-04-27T13:51:39.094Z</v>
+      </c>
+      <c r="C3" t="str">
+        <v>+917567704665</v>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>23</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Hindi</v>
+      </c>
+      <c r="J3" t="str">
+        <v>hi</v>
+      </c>
+      <c r="K3" t="str">
+        <v>English, Gujarati, Hindi</v>
+      </c>
+      <c r="L3" t="str">
         <v>Yes</v>
       </c>
-      <c r="M2" t="str">
+      <c r="M3" t="str">
         <v>Willing to join</v>
       </c>
-      <c r="N2" t="str">
+      <c r="N3" t="str">
         <v>willing_to_join</v>
       </c>
-      <c r="O2" t="str">
+      <c r="O3" t="str">
+        <v>Okay.Thank you.</v>
+      </c>
+      <c r="P3" t="str">
+        <v>CAacaa3411dee890de84d1f51c11ea06b3</v>
+      </c>
+      <c r="Q3" t="str">
+        <v>conv_8301kq7k7b17fzrs5x5eqtea1hkn</v>
+      </c>
+      <c r="R3" t="str" xml:space="preserve">
+        <v xml:space="preserve">Agent: Namaste 
+I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
+Would you be willing to hear a brief message about Maa Umiya and our mission?
+Umiya Dham is being developed as one of the tallest temples in the world, symbolizing strength, devotion, and cultural pride, and spreading a message of unity and spirituality.
+At Vishv Umiya Foundation, the mission is to uplift society through spirituality, education, healthcare, and community service, creating a better and brighter future for all.
+"Thank you for connecting with Vishv Umiya Foundation. We truly value your time. May Maa Umiya...
+Prospect: બસ, બસ, બસ.બસ.
+Agent: ...
+Prospect: वही बोल रहा है।हाँ? वही बोल रहा है। क्या बोल रहा है?
+Agent: [slow] हाँ, मैं...
+Prospect: નહીં, તો મને રૂમ મળી જાય તો.હા. હા, હા.
+Agent: [calm] સમજી ગયા, માફ કરશો. જો તમને રૂમ મળી જાય તો મને જણાવશો?
+Prospect: ...
+Agent: ...
+Prospect: Hello?
+Agent: [soft] हाँ, मैं...
+Prospect: Hello?
+Agent: [calm] हाँ, मैं यहाँ हूँ। क्या आप ठीक हैं?
+Prospect: हाँ, मग बात होऊंगा वो।हाँ।
+Agent: [gentle] बिल्कुल, आपके साथ बात करने के लिए तैयार हूँ। कृपया बताएँ, क्या मदद चाहिए?
+Prospect: मदद कुछ नहीं चाहिए। मुझे यहाँ थोड़ी...
+Agent: [soft] समझ गया। बस थोड़ी देर के लिए आराम कर रहे हैं, ठीक है। मैं यहीं हूँ अगर आपको कुछ चाहिए।
+Prospect: मुझे एक बार phone करना है।
+Agent: [calm] बिल्कुल, आप जब चाहें, फोन कर सकते...
+Prospect: Okay.Thank you.
+Agent: [grateful] You're very welcome. May Maa Umiya bless you with peace and strength. Jai Maa Umiya 🙏
+Prospect: જો ગણી દે.
+Agent: ...</v>
+      </c>
+    </row>
+    <row r="4" xml:space="preserve">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-04-27T13:32:08.933Z</v>
+      </c>
+      <c r="C4" t="str">
+        <v>+919328481970</v>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>23</v>
+      </c>
+      <c r="I4" t="str">
+        <v>Hindi</v>
+      </c>
+      <c r="J4" t="str">
+        <v>hi</v>
+      </c>
+      <c r="K4" t="str">
+        <v>English, Gujarati, Hindi</v>
+      </c>
+      <c r="L4" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M4" t="str">
+        <v>Willing to join</v>
+      </c>
+      <c r="N4" t="str">
+        <v>willing_to_join</v>
+      </c>
+      <c r="O4" t="str">
+        <v>Okay, અ, મેરા નામ હૈ દીપ પટેલ ઔર મેરા mobile number હૈ 9328481970.</v>
+      </c>
+      <c r="P4" t="str">
+        <v>CA70e6c2441b3fafe1be8504050472da6d</v>
+      </c>
+      <c r="Q4" t="str">
+        <v>conv_5101kq7hevw9ez4b7bgmgcbyvn4m</v>
+      </c>
+      <c r="R4" t="str" xml:space="preserve">
+        <v xml:space="preserve">Agent: Namaste 
+I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
+Would you be willing to hear a brief message about Maa Umiya and our mission?...
+Prospect: હા, ઈન હિન્દી.હા, ઈન હિન્દી.
+Agent: [slow] धन्यवाद 🙏आपको हिंदी में संवाद करने में खुशी हुई।क्या आप एक संक्षिप्त संदेश सुनने के लिए तैयार हैं, जो माँ उमिया और विश्व उमिया फाउंडेशन के बारे में...
+Prospect: हाँ।
+Agent: [slow] धन्यवाद 🙏विश्व उमिया फाउंडेशन आध्यात्मिकता, शिक्षा, स्वास्थ्य और समुदाय उत्थान के माध्यम से समाज की सेवा कर रहा है।उमिया धाम दुनिया के सबसे ऊंचे मंदिरों में से एक के रूप में विकसित किया जा रहा है, जो आस्था, एकता और भक्ति का प्रतीक है।क्या आप अधिक जानकारी चाहेंगे या हमारी टीम से जुड़ना चाहेंगे?
+Prospect: मैं अधिक जानकारी भी चाहूंगा और आपकी टीम से जुड़ना भी चाहूंगा।
+Agent: [excited] बहुत अच्छा 🙏आपके संपर्क में आने के लिए धन्यवाद।मैं आपको हमारी टीम से जोड़ दूंगा।कृपया कुछ क्षण प्रतीक्षा करें।[slow] आपको वेबसाइट पर भी जानकारी प्राप्त करने के लिए आमंत्रित करते हैं: https://www.vuf.org/
+Prospect: ...
+Agent: क्या आप यहाँ हैं? क्या मैं आपकी कोई मदद कर सकता...
+Prospect: Yes.
+Agent: [happy] धन्यवाद 🙏आपके साथ बातचीत करके बहुत खुशी हुई।हमारी टीम आपके संपर्क में आएगी जल्द ही।माँ उमिया आप और आपके परिवार को आशीर्वाद दे।शुभ दिन हो।जय माँ उमिया 🙏
+Prospect: ...
+Agent: क्या आप यहाँ हैं? क्या मैं आपकी कोई मदद कर सकता हूँ...
+Agent: Namaste 
+I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
+Would you be willing to hear a brief message about Maa Umiya and our mission?
+Umiya Dham is being developed as one of the tallest temples in the world, symbolizing strength, devotion, and cultural pride, and spreading a message of unity and spirituality.
+At Vishv Umiya Foundation, the mission is to uplift society through spirituality, education, healthcare, and community service, creating a better and brighter f...
+Prospect: હિન્દી.હા.હિન્દી.હા.
+Agent: [slow] धन्यवाद 🙏आपको हिंदी में बात करने में सुविधा होगी।[excited] उमिया धाम दुनिया के सबसे ऊंचे मंदिरों में से एक के रूप में विकसित किया जा रहा है, जो आस्था, एकता और भक्ति का प्रतीक है।[calm] विश्व उमिया फाउंडेशन स्पिरिचुअलिटी, शिक्षा, स्वास्थ्य और समुदाय उन्नयन के माध्यम से समाज की सेवा करता है।क्या आप अधिक जानकारी चाहेंगे या हमारी टीम से जुड़ना चाहेंगे?
+Prospect: हाँ, मैं आपकी टीम से जुड़ना चाहूँगा। क्या process है आपके team के साथ जुड़ने के?
+Agent: [happy] बहुत अच्छा 🙏 आपके साथ जुड़ने के लिए बहुत खुशी हुई।[calm] हम आपको अपनी टीम से जोड़ देंगे, जो आपको विस्तार से बताएगी कि कैसे आप हमारे साथ सहयोग कर सकते हैं।[gentle] कृपया अपना नाम और संपर्क विवरण बताएं, ताकि हम आपके लिए आवेदन प्रक्रिया शुरू कर सकें।
+Prospect: Okay, અ, મેરા નામ હૈ દીપ પટેલ ઔર મેરા mobile number હૈ 9328481970.
+Agent: [grateful] धन्यवाद दीप जी 🙏 आपका नाम और मोबाइल नंबर सफलतापूर्वक दर्ज कर लिया गया है।[calm] हमारी टीम जल्द ही आपके साथ संपर्क करेगी और आपको विस्तार से बताएगी कि कैसे आप हमारे साथ सहयोग कर सकते हैं।[peaceful] आपके समर्थन के लिए फिर से धन्यवाद। माँ उमिया आपकी रक्षा करें और आपके जीवन में शांति भरे। जय माँ उमिया 🙏
+Prospect: जय माँ अम्मिया।धन्यवाद।
+Agent: [peaceful] जय माँ उमिया 🙏 आपका ...
+Prospect: Thank you.</v>
+      </c>
+    </row>
+    <row r="5" xml:space="preserve">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-04-27T12:45:16.133Z</v>
+      </c>
+      <c r="C5" t="str">
+        <v>+917567704665</v>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>27</v>
+      </c>
+      <c r="I5" t="str">
+        <v>Gujarati</v>
+      </c>
+      <c r="J5" t="str">
+        <v>gu</v>
+      </c>
+      <c r="K5" t="str">
+        <v>English, Gujarati, Hindi</v>
+      </c>
+      <c r="L5" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M5" t="str">
+        <v>Willing to join</v>
+      </c>
+      <c r="N5" t="str">
+        <v>willing_to_join</v>
+      </c>
+      <c r="O5" t="str">
         <v>Yes.</v>
       </c>
-      <c r="P2" t="str">
+      <c r="P5" t="str">
         <v>CAc31c80eb3486b26c8ed3c851d5644fcd</v>
       </c>
-      <c r="Q2" t="str">
+      <c r="Q5" t="str">
         <v>conv_9901kq7f5m3ye3hshssbdmbv0bpf</v>
       </c>
-      <c r="R2" t="str" xml:space="preserve">
+      <c r="R5" t="str" xml:space="preserve">
         <v xml:space="preserve">Agent: Namaste 
 I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
 Would you be willing to hear a brief message about Maa Umiya and our mission?
@@ -549,59 +784,59 @@
 Agent: Thank you for your time. Maa Umiya bless you and your family. Have a peaceful day. Jai...</v>
       </c>
     </row>
-    <row r="3" xml:space="preserve">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="str">
+    <row r="6" xml:space="preserve">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="str">
         <v>2026-04-27T11:55:33.786Z</v>
       </c>
-      <c r="C3" t="str">
+      <c r="C6" t="str">
         <v>+917567704665</v>
       </c>
-      <c r="D3" t="str">
-        <v/>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3">
+      <c r="D6" t="str">
+        <v/>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6">
         <v>1</v>
       </c>
-      <c r="H3">
+      <c r="H6">
         <v>5</v>
       </c>
-      <c r="I3" t="str">
+      <c r="I6" t="str">
         <v>English</v>
       </c>
-      <c r="J3" t="str">
+      <c r="J6" t="str">
         <v>en</v>
       </c>
-      <c r="K3" t="str">
+      <c r="K6" t="str">
         <v>English, Gujarati</v>
       </c>
-      <c r="L3" t="str">
+      <c r="L6" t="str">
         <v>No</v>
       </c>
-      <c r="M3" t="str">
+      <c r="M6" t="str">
         <v>Not willing to join</v>
       </c>
-      <c r="N3" t="str">
+      <c r="N6" t="str">
         <v>not_willing_to_join</v>
       </c>
-      <c r="O3" t="str">
+      <c r="O6" t="str">
         <v>No, thank you.</v>
       </c>
-      <c r="P3" t="str">
+      <c r="P6" t="str">
         <v>CA464364dc154700a97ebcc33151fe5dfc</v>
       </c>
-      <c r="Q3" t="str">
+      <c r="Q6" t="str">
         <v>conv_5901kq7cna4efrm8c4pbeqrg76gz</v>
       </c>
-      <c r="R3" t="str" xml:space="preserve">
+      <c r="R6" t="str" xml:space="preserve">
         <v xml:space="preserve">Agent: Namaste 
 Welcome to the divine journey of Maa Umiya at the Vishv Umiya Foundation.
 Umiya Dham is being developed as one of the tallest temples in the world, symbolizing strength, devotion, and cultural pride, and spreading a message of unity and spirituality.
@@ -615,59 +850,59 @@
 Agent: Thank you for your time. Maa Umiya bless you 🙏</v>
       </c>
     </row>
-    <row r="4" xml:space="preserve">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="str">
+    <row r="7" xml:space="preserve">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="str">
         <v>2026-04-27T10:49:11.680Z</v>
       </c>
-      <c r="C4" t="str">
+      <c r="C7" t="str">
         <v>+919586695992</v>
       </c>
-      <c r="D4" t="str">
+      <c r="D7" t="str">
         <v>completed</v>
       </c>
-      <c r="E4" t="str">
+      <c r="E7" t="str">
         <v>+919586695992</v>
       </c>
-      <c r="F4" t="str">
+      <c r="F7" t="str">
         <v>+27872503011</v>
       </c>
-      <c r="G4">
+      <c r="G7">
         <v>1</v>
       </c>
-      <c r="H4">
+      <c r="H7">
         <v>11</v>
       </c>
-      <c r="I4" t="str">
+      <c r="I7" t="str">
         <v>English</v>
       </c>
-      <c r="J4" t="str">
+      <c r="J7" t="str">
         <v>en</v>
       </c>
-      <c r="K4" t="str">
+      <c r="K7" t="str">
         <v>English</v>
       </c>
-      <c r="L4" t="str">
+      <c r="L7" t="str">
         <v>Unknown</v>
       </c>
-      <c r="M4" t="str">
+      <c r="M7" t="str">
         <v>Unknown</v>
       </c>
-      <c r="N4" t="str">
+      <c r="N7" t="str">
         <v>unknown</v>
       </c>
-      <c r="O4" t="str">
+      <c r="O7" t="str">
         <v>The happy.</v>
       </c>
-      <c r="P4" t="str">
+      <c r="P7" t="str">
         <v>CA52bdf5f743c4cbbf3a1ded122a7a9c72</v>
       </c>
-      <c r="Q4" t="str">
+      <c r="Q7" t="str">
         <v>conv_5101kq78v6mxefkrt212jakjny1y</v>
       </c>
-      <c r="R4" t="str" xml:space="preserve">
+      <c r="R7" t="str" xml:space="preserve">
         <v xml:space="preserve">Agent: Namaste 🙏
 Welcome to the divine journey of Maa Umiya at the Vishv Umiya Foundation.
 Umiya Dham is being developed as one of the tallest temples in the world, symbolizing strength, devotion, and cultural pride, and spreading a message of unity and spirituality.
@@ -685,59 +920,59 @@
 Agent: May...</v>
       </c>
     </row>
-    <row r="5" xml:space="preserve">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="str">
+    <row r="8" xml:space="preserve">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="str">
         <v>2026-04-27T10:23:47.984Z</v>
       </c>
-      <c r="C5" t="str">
+      <c r="C8" t="str">
         <v>+917567704665</v>
       </c>
-      <c r="D5" t="str">
+      <c r="D8" t="str">
         <v>completed</v>
       </c>
-      <c r="E5" t="str">
+      <c r="E8" t="str">
         <v>+917567704665</v>
       </c>
-      <c r="F5" t="str">
+      <c r="F8" t="str">
         <v>+27872503011</v>
       </c>
-      <c r="G5">
+      <c r="G8">
         <v>1</v>
       </c>
-      <c r="H5">
+      <c r="H8">
         <v>16</v>
       </c>
-      <c r="I5" t="str">
+      <c r="I8" t="str">
         <v>English</v>
       </c>
-      <c r="J5" t="str">
+      <c r="J8" t="str">
         <v>en</v>
       </c>
-      <c r="K5" t="str">
+      <c r="K8" t="str">
         <v>English</v>
       </c>
-      <c r="L5" t="str">
+      <c r="L8" t="str">
         <v>Yes</v>
       </c>
-      <c r="M5" t="str">
+      <c r="M8" t="str">
         <v>Willing to join</v>
       </c>
-      <c r="N5" t="str">
+      <c r="N8" t="str">
         <v>willing_to_join</v>
       </c>
-      <c r="O5" t="str">
+      <c r="O8" t="str">
         <v>Yes, thank you.</v>
       </c>
-      <c r="P5" t="str">
+      <c r="P8" t="str">
         <v>CAce815922dd7199de06ecc547007b3c76</v>
       </c>
-      <c r="Q5" t="str">
+      <c r="Q8" t="str">
         <v>conv_5801kq778psnfcwar1s2hh303yc1</v>
       </c>
-      <c r="R5" t="str" xml:space="preserve">
+      <c r="R8" t="str" xml:space="preserve">
         <v xml:space="preserve">Agent: Namaste 🙏
 Welcome to the divine journey of Maa Umiya at the Vishv Umiya Foundation.
 Umiya Dham is being developed as one of the tallest temples in the world, symbolizing strength, devotion, and cultural pride, and spreading a message of unity and spirituality.
@@ -763,59 +998,59 @@
 Agent: You're very welcome 🙏 May your journey be filled with peace and divine grace.</v>
       </c>
     </row>
-    <row r="6" xml:space="preserve">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="str">
+    <row r="9" xml:space="preserve">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="str">
         <v>2026-04-27T10:12:44.584Z</v>
       </c>
-      <c r="C6" t="str">
+      <c r="C9" t="str">
         <v>+919328481970</v>
       </c>
-      <c r="D6" t="str">
+      <c r="D9" t="str">
         <v>completed</v>
       </c>
-      <c r="E6" t="str">
+      <c r="E9" t="str">
         <v>+919328481970</v>
       </c>
-      <c r="F6" t="str">
+      <c r="F9" t="str">
         <v>+27872503011</v>
       </c>
-      <c r="G6">
+      <c r="G9">
         <v>1</v>
       </c>
-      <c r="H6">
+      <c r="H9">
         <v>7</v>
       </c>
-      <c r="I6" t="str">
+      <c r="I9" t="str">
         <v>English</v>
       </c>
-      <c r="J6" t="str">
+      <c r="J9" t="str">
         <v>en</v>
       </c>
-      <c r="K6" t="str">
+      <c r="K9" t="str">
         <v>English</v>
       </c>
-      <c r="L6" t="str">
+      <c r="L9" t="str">
         <v>Yes</v>
       </c>
-      <c r="M6" t="str">
+      <c r="M9" t="str">
         <v>Willing to join</v>
       </c>
-      <c r="N6" t="str">
+      <c r="N9" t="str">
         <v>willing_to_join</v>
       </c>
-      <c r="O6" t="str">
+      <c r="O9" t="str">
         <v>Okay, thank you.</v>
       </c>
-      <c r="P6" t="str">
+      <c r="P9" t="str">
         <v>CAa427fe20c39a5478bfa0965b039cdaef</v>
       </c>
-      <c r="Q6" t="str">
+      <c r="Q9" t="str">
         <v>conv_6001kq76qjejf0ate3fgzqkm4p1s</v>
       </c>
-      <c r="R6" t="str" xml:space="preserve">
+      <c r="R9" t="str" xml:space="preserve">
         <v xml:space="preserve">Agent: Namaste 🙏
 Welcome to the divine journey of Maa Umiya at the Vishv Umiya Foundation.
 Umiya Dham is being developed as one of the tallest temples in the world, symbolizing strength, devotion, and cultural pride, and spreading a message of unity and spirituality.
@@ -829,59 +1064,59 @@
 Agent: You're very welcome 🙏May Maa Umiya bless you with peace and joy.Feel free to visit our website anytime to...</v>
       </c>
     </row>
-    <row r="7" xml:space="preserve">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="str">
+    <row r="10" xml:space="preserve">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="str">
         <v>2026-04-21T12:19:57.887Z</v>
       </c>
-      <c r="C7" t="str">
-        <v/>
-      </c>
-      <c r="D7" t="str">
-        <v/>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7">
+      <c r="C10" t="str">
+        <v/>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10">
         <v>1</v>
       </c>
-      <c r="H7">
+      <c r="H10">
         <v>9</v>
       </c>
-      <c r="I7" t="str">
+      <c r="I10" t="str">
         <v>English</v>
       </c>
-      <c r="J7" t="str">
+      <c r="J10" t="str">
         <v>en</v>
       </c>
-      <c r="K7" t="str">
+      <c r="K10" t="str">
         <v>English</v>
       </c>
-      <c r="L7" t="str">
+      <c r="L10" t="str">
         <v>Yes</v>
       </c>
-      <c r="M7" t="str">
+      <c r="M10" t="str">
         <v>Willing to join</v>
       </c>
-      <c r="N7" t="str">
+      <c r="N10" t="str">
         <v>willing_to_join</v>
       </c>
-      <c r="O7" t="str">
+      <c r="O10" t="str">
         <v>Yes, please.</v>
       </c>
-      <c r="P7" t="str">
-        <v/>
-      </c>
-      <c r="Q7" t="str">
+      <c r="P10" t="str">
+        <v/>
+      </c>
+      <c r="Q10" t="str">
         <v>conv_1101kpqznnwhfb19ctz5gqw6hmae</v>
       </c>
-      <c r="R7" t="str" xml:space="preserve">
+      <c r="R10" t="str" xml:space="preserve">
         <v xml:space="preserve">Agent: Hello, this is Desire Infoweb. We help organizations streamline business automation and IT development. Our expertise includes Microsoft Office 365 and AI solutions. If this interests you, we’d be glad to share more.
 Prospect: Yes, I want to know about the services.
 Agent: Great, connecting you to Sajid now.
@@ -893,118 +1128,118 @@
 Agent: I'm here. How can I assist you today?</v>
       </c>
     </row>
-    <row r="8" xml:space="preserve">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="str">
+    <row r="11" xml:space="preserve">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="str">
         <v>2026-04-21T12:18:19.251Z</v>
       </c>
-      <c r="C8" t="str">
-        <v/>
-      </c>
-      <c r="D8" t="str">
-        <v/>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8">
+      <c r="C11" t="str">
+        <v/>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11">
         <v>1</v>
       </c>
-      <c r="H8">
+      <c r="H11">
         <v>4</v>
       </c>
-      <c r="I8" t="str">
+      <c r="I11" t="str">
         <v>English</v>
       </c>
-      <c r="J8" t="str">
+      <c r="J11" t="str">
         <v>en</v>
       </c>
-      <c r="K8" t="str">
+      <c r="K11" t="str">
         <v>English</v>
       </c>
-      <c r="L8" t="str">
+      <c r="L11" t="str">
         <v>Yes</v>
       </c>
-      <c r="M8" t="str">
+      <c r="M11" t="str">
         <v>Willing to join</v>
       </c>
-      <c r="N8" t="str">
+      <c r="N11" t="str">
         <v>willing_to_join</v>
       </c>
-      <c r="O8" t="str">
+      <c r="O11" t="str">
         <v>Yes, please.</v>
       </c>
-      <c r="P8" t="str">
+      <c r="P11" t="str">
         <v>CA971a8c4b5ec935f46fe6347a5143ed47</v>
       </c>
-      <c r="Q8" t="str">
+      <c r="Q11" t="str">
         <v>conv_2101kpqzk1dnf71ttj7f4m79pfdk</v>
       </c>
-      <c r="R8" t="str" xml:space="preserve">
+      <c r="R11" t="str" xml:space="preserve">
         <v xml:space="preserve">Agent: Hello, this is Desire Infoweb. We help organizations streamline business automation and IT development. Our expertise includes Microsoft Office 365 and AI solutions. If this interests you, we’d be glad to share more.
 Prospect: Yes, I want to know about the business automation.
 Agent: Great, connecting you to Sajid now.
 Prospect: Yes, please.</v>
       </c>
     </row>
-    <row r="9" xml:space="preserve">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="str">
+    <row r="12" xml:space="preserve">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="str">
         <v>2026-04-21T05:34:30.564Z</v>
       </c>
-      <c r="C9" t="str">
+      <c r="C12" t="str">
         <v>+919000000001</v>
       </c>
-      <c r="D9" t="str">
+      <c r="D12" t="str">
         <v>completed</v>
       </c>
-      <c r="E9" t="str">
+      <c r="E12" t="str">
         <v>+919000000001</v>
       </c>
-      <c r="F9" t="str">
+      <c r="F12" t="str">
         <v>+278700000001</v>
       </c>
-      <c r="G9">
+      <c r="G12">
         <v>1</v>
       </c>
-      <c r="H9">
+      <c r="H12">
         <v>3</v>
       </c>
-      <c r="I9" t="str">
+      <c r="I12" t="str">
         <v>English</v>
       </c>
-      <c r="J9" t="str">
+      <c r="J12" t="str">
         <v>en</v>
       </c>
-      <c r="K9" t="str">
+      <c r="K12" t="str">
         <v>English</v>
       </c>
-      <c r="L9" t="str">
+      <c r="L12" t="str">
         <v>Unknown</v>
       </c>
-      <c r="M9" t="str">
+      <c r="M12" t="str">
         <v>Unknown</v>
       </c>
-      <c r="N9" t="str">
+      <c r="N12" t="str">
         <v>unknown</v>
       </c>
-      <c r="O9" t="str">
+      <c r="O12" t="str">
         <v>I need details.</v>
       </c>
-      <c r="P9" t="str">
+      <c r="P12" t="str">
         <v>CA11111111111111111111111111111111</v>
       </c>
-      <c r="Q9" t="str">
+      <c r="Q12" t="str">
         <v>conv_full_1</v>
       </c>
-      <c r="R9" t="str" xml:space="preserve">
+      <c r="R12" t="str" xml:space="preserve">
         <v xml:space="preserve">Agent: Hello, thanks for picking up.
 Prospect: I need details.
 Agent: Sure, I can connect you to Sajid.</v>
@@ -1012,7 +1247,7 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R12"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/call-qualifications.xlsx
+++ b/data/call-qualifications.xlsx
@@ -460,7 +460,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-28T04:27:32.498Z</v>
+        <v>2026-04-28T04:34:24.663Z</v>
       </c>
       <c r="C2" t="str">
         <v>+919328481970</v>
@@ -478,28 +478,28 @@
         <v>1</v>
       </c>
       <c r="H2">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="I2" t="str">
-        <v>Hindi</v>
+        <v>English</v>
       </c>
       <c r="J2" t="str">
-        <v>hi</v>
+        <v>en</v>
       </c>
       <c r="K2" t="str">
         <v>English, Gujarati, Hindi</v>
       </c>
       <c r="L2" t="str">
-        <v>Unknown</v>
+        <v>Yes</v>
       </c>
       <c r="M2" t="str">
-        <v>Unknown</v>
+        <v>Willing to join</v>
       </c>
       <c r="N2" t="str">
-        <v>unknown</v>
+        <v>willing_to_join</v>
       </c>
       <c r="O2" t="str">
-        <v>हाँ, please आपकी टीम से जोड़ दीजिए।धन्यवाद।</v>
+        <v>Yes.</v>
       </c>
       <c r="P2" t="str">
         <v>CAca70fdba4d8eb7dad13e25cadb2705e3</v>
@@ -509,6 +509,26 @@
       </c>
       <c r="R2" t="str" xml:space="preserve">
         <v xml:space="preserve">Agent: Namaste 
+I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
+Would you be willing to hear a brief message about Maa Umiya and our mission?
+Umiya Dham is being developed as one of the tallest temples in the world, symbolizing strength, devotion, and cultural pride, and spreading a message of unity and spirituality.
+At Vishv Umiya Foundation, the mission is to uplift society through spirituality, education, healthcare, and community service, creating a better and brighter future for all.
+"Thank you for connecting with Vishv Umiya Foundation. We truly value your time. May Ma...
+Prospect: એક.
+Agent: Thank you 🙏I'm glad you chose Gujarati.Umiya Dham is being developed as one of the tallest temples in the world, symbolizing faith, unity, and devotion.Vishv Umiya Foundation serves society through spirituality, education, healthcare, and community upliftment.Would you like to know more or connect with our team?
+Prospect: Yes, I would like to connect with your team.
+Agent: Wonderful 🙏 I can connect you with our team. Please hold on a moment while I arrange that for you.
+Prospect: ...
+Agent: Hello? Are you still ...
+Prospect: Yes.
+Agent: ...
+Prospect: Uh, yes, I'm still here. Please.
+Agent: Thank you for staying with me 🙏 I'm here to help...
+Prospect: No, about what is the Omnia Dam?
+Agent: I believe you're referring to Umiya Dham, not Omnia Dam. Umiya Dham is being developed as one of the tallest temples in the world, symbolizing faith, unity, and devotion. It is a spiritual and cultural landmark being built by the Vishv Umiya Foundation in Ahmedabad. Would you like to know more about its vision or how it serves society?
+Prospect: Yes.
+Agent: Umiya Dham is being built as a beacon of faith, unity, and cultural heritage, rising as one of the tallest temples in the world. It stands as a symbol of devotion, bringing people together across communities and generations. The temple will also serve as a center for spiritual growth, education, healthcare, and community service through the Vishv Umiya Foundation. Would you like to visit the website to learn more?
+Agent: Namaste 
 I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
 Would you be willing to hear a brief message about Maa Umiya and our mission?
 Umiya Dham is being developed as one of the tallest temples in the world, symbolizing strength, devotion, and cultural pride, and spreading a message of unity and spirituality.

--- a/data/call-qualifications.xlsx
+++ b/data/call-qualifications.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:R3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -460,7 +460,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-28T05:28:57.765Z</v>
+        <v>2026-04-28T05:38:40.915Z</v>
       </c>
       <c r="C2" t="str">
         <v>+919328481970</v>
@@ -478,7 +478,7 @@
         <v>1</v>
       </c>
       <c r="H2">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I2" t="str">
         <v>Hindi</v>
@@ -487,7 +487,7 @@
         <v>hi</v>
       </c>
       <c r="K2" t="str">
-        <v>English, Hindi</v>
+        <v>English, Hindi, Gujarati</v>
       </c>
       <c r="L2" t="str">
         <v>Yes</v>
@@ -499,15 +499,94 @@
         <v>willing_to_join</v>
       </c>
       <c r="O2" t="str">
+        <v>Okay, thank you.</v>
+      </c>
+      <c r="P2" t="str">
+        <v>CAd3fa254243c464a1730f45c7c56505ed</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>conv_5701kq99de98eg794mxra8d73bwb</v>
+      </c>
+      <c r="R2" t="str" xml:space="preserve">
+        <v xml:space="preserve">Agent: Namaste 
+I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
+Would you be willing to hear a brief message about Maa Umiya and our mission?
+Umiya Dham is being developed as one of the tallest temples in the world, symbolizing strength, devotion, and cultural pride, and spreading a message of unity and spirituality.
+At Vishv Umiya Foundation, the mission is to uplift society through spirituality, education, healthcare, and community service, creating a better and brighter future for all.
+"Thank you for connect...
+Prospect: Okay, thank you.
+Agent: You're very...
+Prospect: I am comfortable with the Hindi.
+Agent: धन्यवाद...
+Prospect: સેલોન ની તારીફ કરો.સેલોન ની તારીફ કરો. સેલોન ની �તારીફ કરો. તો ક્યાં?
+Agent: [slow] सेलोन की तारीफ करने के लिए धन्यवाद... लेकिन मैं समझ नहीं पा रहा हूँ कि आप किसकी तारीफ कर रहे हैं? क्या आप मुझे थोड़ा और स्पष्ट बता सकते हैं?
+Prospect: आपने किस लिए call किया है?
+Agent: [calm] मैं विश्व उमिया...
+Prospect: તો તું ખુશ �
+Agent: [happy] हाँ, मैं बहुत खुश हूँ कि आप बात कर रहे हैं। आपके साथ बात करने का मौका मिला, यह बहुत अच्छा लग रहा है।
+Prospect: मुझे आप please वो Umea Foundation के बारे में और detail में बता सकते हैं?
+Agent: [calm] बिल्कुल, आपके लिए खुशी की बात है।विश्व उमिया फाउंडेशन अहमदाबाद में स्थित एक निर्लिप्त संस्था है, जो आध्यात्मिकता, शिक्षा, स्वास्थ्य और समुदाय उत्थान के माध्यम से समाज की सेवा करती है।उमिया धाम दुनिया के सबसे ऊँचे मंदिरों में से एक के रूप में विकसित किया जा रहा है, ...
+Prospect: ये ठीक है।अ, क्या आप बता सकते हैं कि मंदिर से के बारे में कुछ और बता सकते हैं क्या?
+Agent: [calm] हाँ, बिल्कुल।उमिया धाम एक आध्यात्मिक और सांस्कृतिक केंद्र के रूप में विकसित किया जा रहा है, जो विश्व के सबसे ऊँचे मंदिरों में से एक होगा।इसका उद्देश्य भक्ति, एकता और मानवता के संदेश को फैलाना...
+Prospect: उसकी, उसकी height क्या होगी?
+Agent: [calm] उमिया धाम की ऊँचाई लगभग एक हजार फीट होगी, जो दुनिया के सबसे ऊँचे मंदिरों में से एक बनाएगी।यह भक्ति, इतिहास और सांस्कृतिक विरासत का प्रतीक होगा।
+Prospect: ठीक है।
+Agent: ...</v>
+      </c>
+    </row>
+    <row r="3" xml:space="preserve">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-04-28T05:28:57.765Z</v>
+      </c>
+      <c r="C3" t="str">
+        <v>+919328481970</v>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>15</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Hindi</v>
+      </c>
+      <c r="J3" t="str">
+        <v>hi</v>
+      </c>
+      <c r="K3" t="str">
+        <v>English, Hindi</v>
+      </c>
+      <c r="L3" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M3" t="str">
+        <v>Willing to join</v>
+      </c>
+      <c r="N3" t="str">
+        <v>willing_to_join</v>
+      </c>
+      <c r="O3" t="str">
         <v>Yes, जानना चाहूँगा।</v>
       </c>
-      <c r="P2" t="str">
+      <c r="P3" t="str">
         <v>CA34c672f4a33b63610704a7d7f3ade6ab</v>
       </c>
-      <c r="Q2" t="str">
+      <c r="Q3" t="str">
         <v>conv_8201kq98we89eh6v5hpy42ncxkfd</v>
       </c>
-      <c r="R2" t="str" xml:space="preserve">
+      <c r="R3" t="str" xml:space="preserve">
         <v xml:space="preserve">Agent: Namaste 
 I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
 Would you be willing to hear a brief message about Maa Umiya and our mission?
@@ -531,7 +610,7 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/call-qualifications.xlsx
+++ b/data/call-qualifications.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:R12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -460,7 +460,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-28T05:38:40.915Z</v>
+        <v>2026-04-28T08:12:20.478Z</v>
       </c>
       <c r="C2" t="str">
         <v>+919328481970</v>
@@ -478,36 +478,624 @@
         <v>1</v>
       </c>
       <c r="H2">
+        <v>7</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Gujarati</v>
+      </c>
+      <c r="J2" t="str">
+        <v>gu</v>
+      </c>
+      <c r="K2" t="str">
+        <v>English, Gujarati</v>
+      </c>
+      <c r="L2" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M2" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="N2" t="str">
+        <v>unknown</v>
+      </c>
+      <c r="O2" t="str">
+        <v>હા, મારે વધારે જાણવું છે વિશ્વ ઓમિયા foundation ના વિશે.</v>
+      </c>
+      <c r="P2" t="str">
+        <v>CA73824daf7f18e54de49c0bfa20f48f46</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>conv_6801kq9j82gce5087xcrta8mq6y4</v>
+      </c>
+      <c r="R2" t="str" xml:space="preserve">
+        <v xml:space="preserve">Agent: Namaste 
+I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
+Would you be willing to hear a brief message about Maa Umiya a...
+Prospect: હા, એની જોડે.
+Agent: [happy] આભાર, માતા ઉમિયાની સેવામાં આપની સાથે વાત કરવાનું સૌભાગ્ય છે.અમે વિશ્વ ઉમિયા ફાઉન્ડેશન દ્વારા આધ્યાત્મિકતા, શિક્ષણ, સ્વાસ્થ્ય અને સમુદાય ઉન્નતિ માટે કામ કરીએ છીએ.ઊમિયા ધામ વિશ્વની સૌથી ઊંચી મંદિરોમાંનું એક બની રહ્યું છે, જે ભક્તિ, એકતા અને આસ્થાનું પ્રતીક છે.કેમ કે તમે વધુ જાણવા માંગો છો કે અમારી ટીમ સાથે સંપર્ક કરવા માંગો છો?
+Prospect: હા।
+Agent: [excited] સરસ! મારી પાસે તમને અમારી ટીમ સાથે સંપર્ક કરવાની તક છે. કૃપા કરીને થોડી વાત કરો કે તમે કઈ બાબતમાં રસ ધરાવો છો?
+Prospect: હા, મારે વધારે જાણવું છે વિશ્વ ઓમિયા foundation ના વિશે.
+Agent: [calm] આભાર, તમારો રસ માટે ખુબ ખુબ આભાર. વિશ્વ ઉમિયા ફાઉન્ડેશન અમદાવાદમાં આધ્યાત્મિકતા, શિક્ષણ, સ્વાસ્થ્ય અને સમુદાય ઉન્નતિ માટ...</v>
+      </c>
+    </row>
+    <row r="3" xml:space="preserve">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-04-28T08:09:58.868Z</v>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>11</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Gujarati</v>
+      </c>
+      <c r="J3" t="str">
+        <v>gu</v>
+      </c>
+      <c r="K3" t="str">
+        <v>English, Gujarati</v>
+      </c>
+      <c r="L3" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M3" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="N3" t="str">
+        <v>unknown</v>
+      </c>
+      <c r="O3" t="str">
+        <v>જય મા ઉમિયા.</v>
+      </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
+      <c r="Q3" t="str">
+        <v>conv_5801kq9j2ptef53sdz089y7qarx1</v>
+      </c>
+      <c r="R3" t="str" xml:space="preserve">
+        <v xml:space="preserve">Agent: Namaste 
+I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
+Would you be willing to hear a brief message about Maa Umiya and our mission?
+Umiya Dham is being developed as one of the tallest temples in the world, symbolizing strength, devotion, and cultural pride, and spreading a message of unity and spirituality.
+At Vishv Umiya Foundation, the mission is to uplift society through spirituality, education, healthcare, and community service, creating a better and brighter f...
+Prospect: ગુજરાતી.
+Agent: સ્વાગત છે મિત્ર.કૃપા કરીને જણાવો કે તમે કયા ભાષામાં વાત કરવામાં આરામદાયક માનો છો — ગુજરાતી, હિન્દી કે અંગ્રેજી?
+Prospect: ગુજરાતી.
+Agent: ધન્યવાદ, મિત્ર.શું તમે મા ઉમિયા અને વિશ્વ ઉમિયા ફાઉન્ડેશન વિશે થોડી માહિતી સાંભળવા માંગો છો?
+Prospect: હમ્મ, હા, જરૂર.
+Agent: ધન્યવાદ, મિત્ર.યુમિયા ધામ વિશ્વના સૌથી ઊંચા મંદિરોમાંનું એક તરીકે વિકસાવવામાં આવી રહ્યું છે, જે આસ્થા, એકતા અને ભક્તિનું પ્રતીક છે.વિશ્વ ઉમિયા ફાઉન્ડેશન આધ્યાત્મિકતા, શિક્ષણ, સ્વાસ્થ્ય અને સમુદાયની ઉન્નતિ દ્વારા સમાજની સેવા કરે છે.કેમ કે તમે વધુ જાણવા માંગો છો કે અમારી ટીમ સાથે જોડાવા માંગો છો?
+Prospect: અમે જોડાવા માંગીએ છીએ.હા.
+Agent: સરસ! સરસ! મને ખુશી છે કે તમે અમારી ટીમ સાથે જોડાવા માંગો છો.મારી પાસે તમને અમારી ટીમની સંપર્ક માહિતી આપવાની છે.અમારી વેબસાઇટ પર પણ વધુ માહિતી મેળવી શકો છો: https://www.vuf.org/ધન્યવાદ કે તમે વિશ્વ ઉમિયા ફાઉન્ડેશન સાથે જોડાયા.મા ઉમિયા તમને અને તમારા પરિવારને આશીર્વાદ આપે. શુભ દિવસ! જય મા ઉમિયા 🙏
+Prospect: જય મા ઉમિયા.
+Agent: જય મા ઉમિયા! મા ઉમિયા તમને અને તમારા પરિવારને સદા આશીર્વાદ આપે. શુભ દિવસ રહે...</v>
+      </c>
+    </row>
+    <row r="4" xml:space="preserve">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-04-28T08:08:49.302Z</v>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>5</v>
+      </c>
+      <c r="I4" t="str">
+        <v>Gujarati</v>
+      </c>
+      <c r="J4" t="str">
+        <v>gu</v>
+      </c>
+      <c r="K4" t="str">
+        <v>English, Gujarati</v>
+      </c>
+      <c r="L4" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M4" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="N4" t="str">
+        <v>unknown</v>
+      </c>
+      <c r="O4" t="str">
+        <v>ગુજરાતી.</v>
+      </c>
+      <c r="P4" t="str">
+        <v/>
+      </c>
+      <c r="Q4" t="str">
+        <v>conv_0601kq9j10aff04bte8ak7gpqqbx</v>
+      </c>
+      <c r="R4" t="str" xml:space="preserve">
+        <v xml:space="preserve">Agent: Namaste 
+I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
+Would you be willing to hear a brief message about Maa Umiya and our mission?
+Umiya Dham is being developed as one of the tallest temples in the world, symbolizing strength, devotion, and cultural pride, and spreading a message of unity and spirituality.
+At Vishv Umiya Foundation, the mission is to uplift society through spirituality, education, healthcare, and community service, creating a better and brighter future for all.
+"Thank you for connecting with Vishv Umiya Foundation. We truly value your time. May Ma...
+Prospect: ગુજરાતી.
+Agent: સ્વાગત છે.કૃપા કરીને જણાવો કે તમે કયા ભાષામાં વાત કરવામાં આરામદાયક માનો છો — ગુજરાતી, હિન્દી કે અંગ્રેજી?
+Prospect: ગુજરાતી.
+Agent: ધન્યવાદ. મા ઉમિયા અને વિશ્વ ઉમિયા ફાઉન્ડેશન વિશે સંક્ષિપ્ત સમાચાર સાંભળવા તમારી સા...</v>
+      </c>
+    </row>
+    <row r="5" xml:space="preserve">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-04-28T08:04:48.175Z</v>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>13</v>
+      </c>
+      <c r="I5" t="str">
+        <v>Hindi</v>
+      </c>
+      <c r="J5" t="str">
+        <v>hi</v>
+      </c>
+      <c r="K5" t="str">
+        <v>English, Gujarati, Hindi</v>
+      </c>
+      <c r="L5" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M5" t="str">
+        <v>Willing to join</v>
+      </c>
+      <c r="N5" t="str">
+        <v>willing_to_join</v>
+      </c>
+      <c r="O5" t="str">
+        <v>Okay. हाँ, मैं वही हूँ।</v>
+      </c>
+      <c r="P5" t="str">
+        <v/>
+      </c>
+      <c r="Q5" t="str">
+        <v>conv_9201kq9hsbc8egfs31f788amy56w</v>
+      </c>
+      <c r="R5" t="str" xml:space="preserve">
+        <v xml:space="preserve">Agent: Namaste 
+I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
+Would you be willing to hear a brief message about Maa Umiya and our mission?
+Umiya Dham is being developed as one of the tallest temples in the world, symbolizing strength, devotion, and cultural pride, and spreading a message of unity and spirituality.
+At Vishv Umiya Foundation, the mission is to uplift society through spirituality, education, healthcare, and community service, creating a better and brighter future for all.
+"Thank you for connect...
+Prospect: હિન્દી।
+Agent: आपको हिंदी में सहायता करने के लिए बहुत खुशी हुई।क्या आप एक संक्षिप्त संदेश जानने के लिए तैयार हैं, जो माँ उमिया और विश्व उमिया फाउंडेशन के बारे में है?
+Prospect: Yes, हाँ।
+Agent: धन्यवाद। विश्व उमिया फाउंडेशन आध्यात्मिकता, शिक्षा, स्वास्थ्य और समुदाय उत्थान के माध्यम से समाज की सेवा करता है।उमिया धाम दुनिया के सबसे ऊंचे मंदिरों में से एक के रूप में विकसित किया जा रहा है, जो आस्था, एकता और भक्ति का प्रतीक है।क्या आप अधिक जानकारी चाहते हैं या हमारी टीम से जुड़ना चाहते हैं?
+Prospect: हम आपकी टीम से जुड़ना चाहते हैं।
+Agent: वाह बहुत अच्छा! आपको हमारी टीम से जुड़ने के लिए बहुत धन्यवाद। मैं आपको तुरंत जोड़ दूंगा।[excited] आपका संपर्क बहुत महत्वपूर्ण है।कृपया थोड़ा इंतजार करें, मैं आपको जुड़ा रहा हूँ।[slow]
+Prospect: ...
+Agent: क्या आप...
+Prospect: Okay. हाँ, मैं वही हूँ।
+Agent: धन्यवाद आपके समय के लिए।[happy] आपको विश्व उमिया फाउंडेशन के साथ जुड़ने के लिए बहुत बधाई।[slow] हमारी टीम आपके संपर्क में आएगी जल्द ही।[peaceful] आपके जीवन में शांति और आनंद बना रहे।जय माँ उमिया 🙏
+Prospect: धन्यवाद।
+Agent: आपका स्वागत है।[grateful] माँ उमिया आपके और आपके परिवार के जीवन में शांति और सुख लाएं।[peaceful] आपका दिन शुभ हो।जय माँ उमिया 🙏</v>
+      </c>
+    </row>
+    <row r="6" xml:space="preserve">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-04-28T08:02:30.875Z</v>
+      </c>
+      <c r="C6" t="str">
+        <v/>
+      </c>
+      <c r="D6" t="str">
+        <v/>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>9</v>
+      </c>
+      <c r="I6" t="str">
+        <v>English</v>
+      </c>
+      <c r="J6" t="str">
+        <v>en</v>
+      </c>
+      <c r="K6" t="str">
+        <v>English, Gujarati, Hindi</v>
+      </c>
+      <c r="L6" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M6" t="str">
+        <v>Willing to join</v>
+      </c>
+      <c r="N6" t="str">
+        <v>willing_to_join</v>
+      </c>
+      <c r="O6" t="str">
+        <v>Okay. Sir.</v>
+      </c>
+      <c r="P6" t="str">
+        <v/>
+      </c>
+      <c r="Q6" t="str">
+        <v>conv_5901kq9hptgbe6rt4tjjqhnfmwk3</v>
+      </c>
+      <c r="R6" t="str" xml:space="preserve">
+        <v xml:space="preserve">Agent: Namaste 
+I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
+Would you be ...
+Prospect: હમ્મ, ગુજરાતી.
+Agent: ...
+Prospect: Okay. Sir.
+Agent: સારું, માનનીય મહોદય.શું તમે મા ઉમિયા અને વિશ્વ ઉમિયા ફાઉન્ડેશન વિશે સંક્ષિપ્ત સમાચાર સાંભળવા તૈયાર છો?
+Prospect: Hello?
+Agent: હા, હા માનનીય મહોદય. હું છું વિશ્વ ઉમિયા ફાઉન્ડેશનની તરફથી. કૃપા કરીને જણાવો કે તમે કઈ ભાષામાં વાત કરવામાં આરામદાયક માનો છો? ઇંગ્લિશ, હિન્દી કે ગુજરાતી?...
+Prospect: હિન્દી.
+Agent: सारा, महोदय। क्या आप माँ उमिया और विश्व उमिया फाउंडेशन के बारे में एक संक्षिप्त संदेश सुनने के लिए तैयार हैं?</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-04-28T06:42:54.419Z</v>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7" t="str">
+        <v>English</v>
+      </c>
+      <c r="J7" t="str">
+        <v>en</v>
+      </c>
+      <c r="K7" t="str">
+        <v>English</v>
+      </c>
+      <c r="L7" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M7" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="N7" t="str">
+        <v>unknown</v>
+      </c>
+      <c r="O7" t="str">
+        <v>Transcript: Summary couldn't be generated for this call.</v>
+      </c>
+      <c r="P7" t="str">
+        <v/>
+      </c>
+      <c r="Q7" t="str">
+        <v>conv_7301kq9d735ve92stwtsszksq7v2</v>
+      </c>
+      <c r="R7" t="str">
+        <v>Transcript: Summary couldn't be generated for this call.</v>
+      </c>
+    </row>
+    <row r="8" xml:space="preserve">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-04-28T06:42:53.484Z</v>
+      </c>
+      <c r="C8" t="str">
+        <v/>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>9</v>
+      </c>
+      <c r="I8" t="str">
+        <v>Gujarati</v>
+      </c>
+      <c r="J8" t="str">
+        <v>gu</v>
+      </c>
+      <c r="K8" t="str">
+        <v>English, Gujarati</v>
+      </c>
+      <c r="L8" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M8" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="N8" t="str">
+        <v>unknown</v>
+      </c>
+      <c r="O8" t="str">
+        <v>હા</v>
+      </c>
+      <c r="P8" t="str">
+        <v/>
+      </c>
+      <c r="Q8" t="str">
+        <v>conv_9001kq9cx1bceky9cfvjzpq4tc09</v>
+      </c>
+      <c r="R8" t="str" xml:space="preserve">
+        <v xml:space="preserve">Agent: Namaste 
+I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
+Would you be willing to hear a brief message about Maa Umiya and our mission?
+Umiya Dham is being developed as one of the tallest temples in the world, symbolizing strength, devotion, and cultural pride, and spreading a message of unity and spirituality.
+At Vishv Umiya Foundation, the mission is to uplift society through spirituality, education, healthcare, and community service, creating a better and brighter future for all.
+"Thank you for connecting with Vishv Umiya Foundation. We truly value your time. May Maa Umiya bless you and you...
+Prospect: હેલો
+Agent: હેલો મિત્ર, કૃપા કરીને કહો કે તમે કયા ભાષામાં સાથે વાત કરવામાં આનંદ માણી શકો છો — ગુજરાતી, હિન્દી કે અંગ્રેજી?
+Prospect: હેલો
+Agent: હેલો મિત્ર, કૃપા કરીને કહો કે તમે કયા ભાષામાં સાથે વાત કરવામાં આનંદ માણી શકો છો — ગુજરાતી, હિન્દી કે અંગ્રેજી?
+Prospect: ગુજરાતી
+Agent: ધન્યવાદ, ગુજરાતીમાં વાત કરવા માટે આભાર 🙏કૃપા કરીને જણાવો, શું તમે મા ઉમિયા અને વિશ્વ ઉમિયા ફાઉન્ડેશનની સંક્ષિપ્ત માહિતી સાંભળવા માંગો છો?
+Prospect: હા
+Agent: ધન્યવાદ 🙏યુમિયા ધામ વિશ્વના સૌથી ઊંચા મંદિરોમાંના એક તરીકે વિકસાવવામાં આવી રહ્યું છે, જે આસ્થા, એકતા અને ભક્તિનું પ્રતીક છે.વિશ્વ ઉમિયા ફાઉન્ડેશન આધ્યાત્મિકતા, શિક્ષણ, સ્વાસ્...</v>
+      </c>
+    </row>
+    <row r="9" xml:space="preserve">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-04-28T06:31:37.032Z</v>
+      </c>
+      <c r="C9" t="str">
+        <v/>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9" t="str">
+        <v>English</v>
+      </c>
+      <c r="J9" t="str">
+        <v>en</v>
+      </c>
+      <c r="K9" t="str">
+        <v>English</v>
+      </c>
+      <c r="L9" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M9" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="N9" t="str">
+        <v>unknown</v>
+      </c>
+      <c r="O9" t="str" xml:space="preserve">
+        <v xml:space="preserve">Agent: Namaste 
+I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
+Would you be willing to hear a brief message about Maa Umiya and our mission?
+Umiya Dham is being develope</v>
+      </c>
+      <c r="P9" t="str">
+        <v/>
+      </c>
+      <c r="Q9" t="str">
+        <v>conv_8301kq9chf18f59barx86mgyqn9a</v>
+      </c>
+      <c r="R9" t="str" xml:space="preserve">
+        <v xml:space="preserve">Agent: Namaste 
+I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
+Would you be willing to hear a brief message about Maa Umiya and our mission?
+Umiya Dham is being developed as one of the tallest temples in the world, symbolizing strength, devotion, and cultural pride, and spreading a message of unity and spirituality.
+At Vishv Umiya Foundation, the mission is to uplift society through ...</v>
+      </c>
+    </row>
+    <row r="10" xml:space="preserve">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-04-28T06:30:38.685Z</v>
+      </c>
+      <c r="C10" t="str">
+        <v/>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10" t="str">
+        <v>English</v>
+      </c>
+      <c r="J10" t="str">
+        <v>en</v>
+      </c>
+      <c r="K10" t="str">
+        <v>English</v>
+      </c>
+      <c r="L10" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M10" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="N10" t="str">
+        <v>unknown</v>
+      </c>
+      <c r="O10" t="str" xml:space="preserve">
+        <v xml:space="preserve">Agent: Namaste 
+I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
+Would you be willing to hear a brief message about Maa Umiya and our mission?
+Umiya Dham is being develope</v>
+      </c>
+      <c r="P10" t="str">
+        <v/>
+      </c>
+      <c r="Q10" t="str">
+        <v>conv_6701kq9cg2eqer287bf4msmr1rhh</v>
+      </c>
+      <c r="R10" t="str" xml:space="preserve">
+        <v xml:space="preserve">Agent: Namaste 
+I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
+Would you be willing to hear a brief message about Maa Umiya and our mission?
+Umiya Dham is being developed as one...</v>
+      </c>
+    </row>
+    <row r="11" xml:space="preserve">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-04-28T05:38:40.915Z</v>
+      </c>
+      <c r="C11" t="str">
+        <v>+919328481970</v>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
         <v>19</v>
       </c>
-      <c r="I2" t="str">
+      <c r="I11" t="str">
         <v>Hindi</v>
       </c>
-      <c r="J2" t="str">
+      <c r="J11" t="str">
         <v>hi</v>
       </c>
-      <c r="K2" t="str">
+      <c r="K11" t="str">
         <v>English, Hindi, Gujarati</v>
       </c>
-      <c r="L2" t="str">
+      <c r="L11" t="str">
         <v>Yes</v>
       </c>
-      <c r="M2" t="str">
+      <c r="M11" t="str">
         <v>Willing to join</v>
       </c>
-      <c r="N2" t="str">
+      <c r="N11" t="str">
         <v>willing_to_join</v>
       </c>
-      <c r="O2" t="str">
+      <c r="O11" t="str">
         <v>Okay, thank you.</v>
       </c>
-      <c r="P2" t="str">
+      <c r="P11" t="str">
         <v>CAd3fa254243c464a1730f45c7c56505ed</v>
       </c>
-      <c r="Q2" t="str">
+      <c r="Q11" t="str">
         <v>conv_5701kq99de98eg794mxra8d73bwb</v>
       </c>
-      <c r="R2" t="str" xml:space="preserve">
+      <c r="R11" t="str" xml:space="preserve">
         <v xml:space="preserve">Agent: Namaste 
 I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
 Would you be willing to hear a brief message about Maa Umiya and our mission?
@@ -534,59 +1122,59 @@
 Agent: ...</v>
       </c>
     </row>
-    <row r="3" xml:space="preserve">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="str">
+    <row r="12" xml:space="preserve">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="str">
         <v>2026-04-28T05:28:57.765Z</v>
       </c>
-      <c r="C3" t="str">
+      <c r="C12" t="str">
         <v>+919328481970</v>
       </c>
-      <c r="D3" t="str">
-        <v/>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
+      <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
         <v>15</v>
       </c>
-      <c r="I3" t="str">
+      <c r="I12" t="str">
         <v>Hindi</v>
       </c>
-      <c r="J3" t="str">
+      <c r="J12" t="str">
         <v>hi</v>
       </c>
-      <c r="K3" t="str">
+      <c r="K12" t="str">
         <v>English, Hindi</v>
       </c>
-      <c r="L3" t="str">
+      <c r="L12" t="str">
         <v>Yes</v>
       </c>
-      <c r="M3" t="str">
+      <c r="M12" t="str">
         <v>Willing to join</v>
       </c>
-      <c r="N3" t="str">
+      <c r="N12" t="str">
         <v>willing_to_join</v>
       </c>
-      <c r="O3" t="str">
+      <c r="O12" t="str">
         <v>Yes, जानना चाहूँगा।</v>
       </c>
-      <c r="P3" t="str">
+      <c r="P12" t="str">
         <v>CA34c672f4a33b63610704a7d7f3ade6ab</v>
       </c>
-      <c r="Q3" t="str">
+      <c r="Q12" t="str">
         <v>conv_8201kq98we89eh6v5hpy42ncxkfd</v>
       </c>
-      <c r="R3" t="str" xml:space="preserve">
+      <c r="R12" t="str" xml:space="preserve">
         <v xml:space="preserve">Agent: Namaste 
 I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
 Would you be willing to hear a brief message about Maa Umiya and our mission?
@@ -610,7 +1198,7 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R12"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/call-qualifications.xlsx
+++ b/data/call-qualifications.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R12"/>
+  <dimension ref="A1:R21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -460,10 +460,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-28T08:12:20.478Z</v>
+        <v>2026-04-28T10:09:01.826Z</v>
       </c>
       <c r="C2" t="str">
-        <v>+919328481970</v>
+        <v/>
       </c>
       <c r="D2" t="str">
         <v/>
@@ -478,7 +478,7 @@
         <v>1</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I2" t="str">
         <v>Gujarati</v>
@@ -499,15 +499,592 @@
         <v>unknown</v>
       </c>
       <c r="O2" t="str">
+        <v>ના.</v>
+      </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+      <c r="Q2" t="str">
+        <v>conv_9101kq9rx3nbf3hsqrspc9b7zk5q</v>
+      </c>
+      <c r="R2" t="str" xml:space="preserve">
+        <v xml:space="preserve">Agent: Namaste 
+I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
+Would you be...
+Prospect: Gujarati.
+Agent: સ્વાગત છે.શું તમે મા ઉમિયા અને વિશ્વ ઉમિયા ફાઉન્ડેશન વિશે સંક્ષિપ્ત સંદેશ સાંભળવા માંગો છો?
+Prospect: હા।
+Agent: ધન્યવાદ. ઉમિયા ધામ વિશ્વના સૌથી ઊંચા મંદિરોમાંના એક તરીકે વિકસાવવામાં આવી રહ્યું છે, જે ભક્તિ, એકતા અને આસ્થાનું પ્રતીક છે.વિશ્વ ઉમિયા ફાઉન્ડેશન આધ્યાત્મિકતા, શિક્ષણ, સ્વાસ્થ્ય અને સમુદાયની ઉન્નતિ દ્વારા સમાજની સેવા કરે છે.કેમ કે તમે વધુ જાણવા માંગો છો કે અમારી ટીમ સાથે જોડાવા માંગો છો?
+Prospect: હમ, વધુ જાણવા માંગીએ છીએ.હમ, વધુ જાણવા માંગીએ છીએ.
+Agent: સરસ! વિશ્વ ઉમિયા ફાઉન્ડેશન આધ્યાત્મિકતા, શિક્ષણ, સ્વાસ્થ્ય અને સમુદાયની ઉન્નતિ દ્વારા સમાજની સેવા કરે છે. ઉમિયા ધામ વિશ્વના સૌથી ઊંચા મંદિરોમાંના એક તરીકે વિકસાવવામાં આવી રહ્યું છે, જે ભક્તિ, એકતા અને આસ્થાનું પ્રતીક છે. વધુ માહિતી માટે આપણી વેબસાઇટ પર જોવા માટે આવો: https://www.vuf.org/ કે અમારી ટીમ સાથે જોડાવા માંગો છો?
+Prospect: ના.
+Agent: ...</v>
+      </c>
+    </row>
+    <row r="3" xml:space="preserve">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-04-28T10:06:59.684Z</v>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>5</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Hindi</v>
+      </c>
+      <c r="J3" t="str">
+        <v>hi</v>
+      </c>
+      <c r="K3" t="str">
+        <v>English, Hindi</v>
+      </c>
+      <c r="L3" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M3" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="N3" t="str">
+        <v>unknown</v>
+      </c>
+      <c r="O3" t="str">
+        <v>हाँ, मैं अधिक जानना चाहूंगा।</v>
+      </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
+      <c r="Q3" t="str">
+        <v>conv_7601kq9rv4d2e9rrjrjwdbm3b48p</v>
+      </c>
+      <c r="R3" t="str" xml:space="preserve">
+        <v xml:space="preserve">Agent: Namaste 
+I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
+Would you be willing to hear a brief messa...
+Prospect: Hindi.
+Agent: धन्यवाद।उमिया धाम विश्व के सबसे ऊंचे मंदिरों में से एक के रूप में विकसित किया जा रहा है, जो आस्था, एकता और भक्ति का प्रतीक है।विश्व उमिया फाउंडेशन स्पिरिचुअलिटी, शिक्षा, स्वास्थ्य और समुदाय उन्नयन के माध्यम से समाज की सेवा करता है।क्या आप अधिक जानना चाहेंगे या हमारी टीम से जुड़ना चाहेंगे?
+Prospect: हाँ, मैं अधिक जानना चाहूंगा।
+Agent: [excited] बहुत अच्छा! आप वेबसाइट पर अधिक जानकारी प्राप्त कर सकते हैं: https://www.vuf.org/क्या आप अपने...</v>
+      </c>
+    </row>
+    <row r="4" xml:space="preserve">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-04-28T10:01:48.637Z</v>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>7</v>
+      </c>
+      <c r="I4" t="str">
+        <v>Gujarati</v>
+      </c>
+      <c r="J4" t="str">
+        <v>gu</v>
+      </c>
+      <c r="K4" t="str">
+        <v>English, Gujarati</v>
+      </c>
+      <c r="L4" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M4" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="N4" t="str">
+        <v>unknown</v>
+      </c>
+      <c r="O4" t="str">
+        <v>હા।</v>
+      </c>
+      <c r="P4" t="str">
+        <v/>
+      </c>
+      <c r="Q4" t="str">
+        <v>conv_5701kq9rh34nfy9s02fpz6mb9cng</v>
+      </c>
+      <c r="R4" t="str" xml:space="preserve">
+        <v xml:space="preserve">Agent: Namaste 
+I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
+Would you be willing to hear a ...
+Prospect: Gujarat.
+Agent: સ્વાગત છે!કૃપા કરીને જણાવો કે તમે કયા ભાષામાં વાત કરવામાં આરામદાયક માનો છો — અંગ્રેજી, હિન્દી, કે ગુજરાતી?
+Prospect: ગુજરાતી.
+Agent: સ્વાગત છે!અમારી સેવાઓ વિશે થોડો સમય લઈને સાંભળવા તમારી સાથે વાત કરવા તમારી તૈયારી છે?
+Prospect: હા।
+Agent: ધન્યવાદ. ઉમિયા ધામ વિશ્વના સૌથી ઊંચા મંદિરોમાંના એક તરીકે વિકસાવવામાં આવી રહ્યું છે, જે ભક્તિ, એકતા અને આધ્યાત્મિકતાનું પ્રતીક છે.વિશ્વ ઉમિયા ફાઉન્ડેશન આધ્યાત્મિકતા, શિક્ષણ, સ્વાસ્થ્ય અને સમાજની ઉન્નતિ દ્વારા સમાજની સેવા કરે છે.કેમ કે તમને વધુ જાણવા માંગો છો કે અમારી ટીમ સાથે જોડાવા માંગો છો?</v>
+      </c>
+    </row>
+    <row r="5" xml:space="preserve">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-04-28T09:49:46.217Z</v>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>5</v>
+      </c>
+      <c r="I5" t="str">
+        <v>Gujarati</v>
+      </c>
+      <c r="J5" t="str">
+        <v>gu</v>
+      </c>
+      <c r="K5" t="str">
+        <v>English, Gujarati</v>
+      </c>
+      <c r="L5" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M5" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="N5" t="str">
+        <v>unknown</v>
+      </c>
+      <c r="O5" t="str">
+        <v>...</v>
+      </c>
+      <c r="P5" t="str">
+        <v/>
+      </c>
+      <c r="Q5" t="str">
+        <v>conv_2601kq9qvs1jebds4t54m74mvpkt</v>
+      </c>
+      <c r="R5" t="str" xml:space="preserve">
+        <v xml:space="preserve">Agent: Namaste 
+I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
+Would you be willing to hear...
+Prospect: હિન્દુ.
+Agent: સારું છે, હું હિન્દીમાં વાત કરીશ।કૃપા કરીને જણાવો કે કેટલો સમય તમને લાગે છે?[slow] મેં તમને માતા ઉમિયા અને વિશ્વ ઉમિયા ફાઉન્ડેશન વિશે થોડી માહિતી આપવા માંગુ છું।
+Prospect: ...
+Agent: કૃપા કરીને જણાવો, કે કેટલો સમય તમને લાગે છે?[slow] મેં તમને માતા ઉમિયા અને વિશ્વ ઉમિયા ફાઉન્ડેશન વિશે થોડી માહિતી આપવા માંગુ છું।...</v>
+      </c>
+    </row>
+    <row r="6" xml:space="preserve">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-04-28T09:43:59.661Z</v>
+      </c>
+      <c r="C6" t="str">
+        <v/>
+      </c>
+      <c r="D6" t="str">
+        <v/>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6" t="str">
+        <v>English</v>
+      </c>
+      <c r="J6" t="str">
+        <v>en</v>
+      </c>
+      <c r="K6" t="str">
+        <v>English</v>
+      </c>
+      <c r="L6" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M6" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="N6" t="str">
+        <v>unknown</v>
+      </c>
+      <c r="O6" t="str" xml:space="preserve">
+        <v xml:space="preserve">Agent: Namaste 
+I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
+Would you be willing to hear a brief message about Maa Umiya and our mission?
+Umiya Dham is being develope</v>
+      </c>
+      <c r="P6" t="str">
+        <v/>
+      </c>
+      <c r="Q6" t="str">
+        <v>conv_3701kq9qgpj7fx5vbjnb0k742b1d</v>
+      </c>
+      <c r="R6" t="str" xml:space="preserve">
+        <v xml:space="preserve">Agent: Namaste 
+I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
+Would you be willing to hear a brief message about Maa Umiya and our mission?
+Umiya Dham is being developed as one of the tallest temples in the world, symbolizing strength, devotion, and cultural pride, and spreading a message of unity and spirituality.
+At Vishv Umiya Foundation, the mission is to uplift society through spirituality, education, healthcare, and community service, creating a better and brighter future for all.
+"Thank you for connecting with Vishv Umiya Foundation. We truly value your time. May Maa Umiya bless you and your family. Have a wonderful day...</v>
+      </c>
+    </row>
+    <row r="7" xml:space="preserve">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-04-28T09:43:34.372Z</v>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7" t="str">
+        <v>Gujarati</v>
+      </c>
+      <c r="J7" t="str">
+        <v>gu</v>
+      </c>
+      <c r="K7" t="str">
+        <v>English, Gujarati</v>
+      </c>
+      <c r="L7" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M7" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="N7" t="str">
+        <v>unknown</v>
+      </c>
+      <c r="O7" t="str">
+        <v>...</v>
+      </c>
+      <c r="P7" t="str">
+        <v/>
+      </c>
+      <c r="Q7" t="str">
+        <v>conv_3201kq9qgyvae3sby1cd2k9d91wx</v>
+      </c>
+      <c r="R7" t="str" xml:space="preserve">
+        <v xml:space="preserve">Agent: Namaste 
+I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
+Would you be willing to hear a brief message about Maa Umiya and our mission?
+Umiya Dham is being developed as one of...
+Prospect: હાં.
+Agent: [happy] ધન્યવાદ! કૃપા કરીને કહો કે તમે કયા ભાષામાં સુવિધા માટે આરામથી બોલવા માંગો છો — અંગ્રેજી, હિન્દી કે ગુજરાતી?
+Prospect: ...
+Agent: [soft] હું સમજું...</v>
+      </c>
+    </row>
+    <row r="8" xml:space="preserve">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-04-28T09:41:51.754Z</v>
+      </c>
+      <c r="C8" t="str">
+        <v/>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>7</v>
+      </c>
+      <c r="I8" t="str">
+        <v>English</v>
+      </c>
+      <c r="J8" t="str">
+        <v>en</v>
+      </c>
+      <c r="K8" t="str">
+        <v>English, Gujarati</v>
+      </c>
+      <c r="L8" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M8" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="N8" t="str">
+        <v>unknown</v>
+      </c>
+      <c r="O8" t="str">
+        <v>Thank you.</v>
+      </c>
+      <c r="P8" t="str">
+        <v/>
+      </c>
+      <c r="Q8" t="str">
+        <v>conv_9401kq9qd86qea2rg6xtnzj9fw5s</v>
+      </c>
+      <c r="R8" t="str" xml:space="preserve">
+        <v xml:space="preserve">Agent: Namaste 
+I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
+Would you be willing ...
+Prospect: નહીં.
+Agent: Thank you for your time. Maa Umiya bless you and your family. Have a peaceful day. Jai Maa Umiya 🙏
+Prospect: શું? તમને શું લાગે છે?તમને શું લાગે છે?તમે બોલવાનું જ ચાલુ કરો છો. હમ્મ.તમે બોલવાનું જ ચાલુ કરો છ
+Agent: ...
+Prospect: Thank you.
+Agent: You're welcome. May Maa Umiya bless you and your family. Have a wonderful da...</v>
+      </c>
+    </row>
+    <row r="9" xml:space="preserve">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-04-28T09:40:49.805Z</v>
+      </c>
+      <c r="C9" t="str">
+        <v/>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>3</v>
+      </c>
+      <c r="I9" t="str">
+        <v>English</v>
+      </c>
+      <c r="J9" t="str">
+        <v>en</v>
+      </c>
+      <c r="K9" t="str">
+        <v>English</v>
+      </c>
+      <c r="L9" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M9" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="N9" t="str">
+        <v>unknown</v>
+      </c>
+      <c r="O9" t="str">
+        <v>Hello?</v>
+      </c>
+      <c r="P9" t="str">
+        <v/>
+      </c>
+      <c r="Q9" t="str">
+        <v>conv_3701kq9qc50jf66b0kyccx2f2687</v>
+      </c>
+      <c r="R9" t="str" xml:space="preserve">
+        <v xml:space="preserve">Agent: Namaste 
+I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
+Would you be willing to hear a brief message about Maa Umiya and our mission?
+Umiya Dham is being developed as one of the tallest temples in the world, symbolizing strength, devotion, a...
+Prospect: Hello?
+Agent: Hello, I'm here.Would you be willing to hear a brief message about Maa Umiya and Vishv Umiya Foundation?</v>
+      </c>
+    </row>
+    <row r="10" xml:space="preserve">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-04-28T09:40:25.307Z</v>
+      </c>
+      <c r="C10" t="str">
+        <v/>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>11</v>
+      </c>
+      <c r="I10" t="str">
+        <v>English</v>
+      </c>
+      <c r="J10" t="str">
+        <v>en</v>
+      </c>
+      <c r="K10" t="str">
+        <v>English, Hindi, Gujarati</v>
+      </c>
+      <c r="L10" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M10" t="str">
+        <v>Willing to join</v>
+      </c>
+      <c r="N10" t="str">
+        <v>willing_to_join</v>
+      </c>
+      <c r="O10" t="str">
+        <v>Yes.</v>
+      </c>
+      <c r="P10" t="str">
+        <v/>
+      </c>
+      <c r="Q10" t="str">
+        <v>conv_9701kq9q8j4yftes3c09h4h0z6hs</v>
+      </c>
+      <c r="R10" t="str" xml:space="preserve">
+        <v xml:space="preserve">Agent: Namaste 
+I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
+Would you be willing to hear a brief message about Maa Umiya and our mission?
+Umiya Dham is being developed as one of the tallest temples in the world, symbolizing strength, devotion, and cultural pride, and spreading a message of unity and spirituality.
+At Vishv Umiya Foundation, the mission is to uplift society through spirituality, education, healthcare, and community service, creating a better and brighter future for all.
+"Thank you for connecting with Vishv Umiya Foundation. We truly value your time. May Maa Umiya bless you and you...
+Prospect: PC अभी तो यही है।अच्छा।
+Agent: [slow] Thank you for your response.Would you like to know more about Umiya Dham and how the foundation is serving society through faith and service?
+Prospect: શું જરા થી?થોડું થોડું.
+Agent: [soft] Thank you for sharing. Would you like to know how Umiya Dham is being built as a symbol of devotion and unity, and how the Vishv Umiya Foundation supports education, healthcare, and community upliftment?
+Prospect: Yes.
+Agent: [calm] Umiya Dham is being developed as one of the tallest temples in the world, representing faith, unity, and spiritual strength.The Vishv Umiya Foundation serves society through education, healthcare, and community programs, spreading love and service.Would you like to visit our website to learn more? It’s https://www.vuf.org/
+Prospect: Yes.
+Agent: [gentle] Wonderful I’m glad you’re interested. You can visit our website at https://www.vuf.org/ to explore more about Umiya Dham and the foundation’s work.Would you like me to connect you with our team for further details?
+Prospect: Yes.
+Agent: [pleasant] Wonderful I’ll connect you with our team right away. Thank you for your time and interest in Vishv Umiya Foundation. May Maa Umiya bless you and your family. Have a wonderful day. Jai Maa Umiya 🙏</v>
+      </c>
+    </row>
+    <row r="11" xml:space="preserve">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-04-28T08:12:20.478Z</v>
+      </c>
+      <c r="C11" t="str">
+        <v>+919328481970</v>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>7</v>
+      </c>
+      <c r="I11" t="str">
+        <v>Gujarati</v>
+      </c>
+      <c r="J11" t="str">
+        <v>gu</v>
+      </c>
+      <c r="K11" t="str">
+        <v>English, Gujarati</v>
+      </c>
+      <c r="L11" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M11" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="N11" t="str">
+        <v>unknown</v>
+      </c>
+      <c r="O11" t="str">
         <v>હા, મારે વધારે જાણવું છે વિશ્વ ઓમિયા foundation ના વિશે.</v>
       </c>
-      <c r="P2" t="str">
+      <c r="P11" t="str">
         <v>CA73824daf7f18e54de49c0bfa20f48f46</v>
       </c>
-      <c r="Q2" t="str">
+      <c r="Q11" t="str">
         <v>conv_6801kq9j82gce5087xcrta8mq6y4</v>
       </c>
-      <c r="R2" t="str" xml:space="preserve">
+      <c r="R11" t="str" xml:space="preserve">
         <v xml:space="preserve">Agent: Namaste 
 I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
 Would you be willing to hear a brief message about Maa Umiya a...
@@ -519,59 +1096,59 @@
 Agent: [calm] આભાર, તમારો રસ માટે ખુબ ખુબ આભાર. વિશ્વ ઉમિયા ફાઉન્ડેશન અમદાવાદમાં આધ્યાત્મિકતા, શિક્ષણ, સ્વાસ્થ્ય અને સમુદાય ઉન્નતિ માટ...</v>
       </c>
     </row>
-    <row r="3" xml:space="preserve">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="str">
+    <row r="12" xml:space="preserve">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="str">
         <v>2026-04-28T08:09:58.868Z</v>
       </c>
-      <c r="C3" t="str">
-        <v/>
-      </c>
-      <c r="D3" t="str">
-        <v/>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
+      <c r="C12" t="str">
+        <v/>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
         <v>11</v>
       </c>
-      <c r="I3" t="str">
+      <c r="I12" t="str">
         <v>Gujarati</v>
       </c>
-      <c r="J3" t="str">
+      <c r="J12" t="str">
         <v>gu</v>
       </c>
-      <c r="K3" t="str">
+      <c r="K12" t="str">
         <v>English, Gujarati</v>
       </c>
-      <c r="L3" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="M3" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="N3" t="str">
+      <c r="L12" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M12" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="N12" t="str">
         <v>unknown</v>
       </c>
-      <c r="O3" t="str">
+      <c r="O12" t="str">
         <v>જય મા ઉમિયા.</v>
       </c>
-      <c r="P3" t="str">
-        <v/>
-      </c>
-      <c r="Q3" t="str">
+      <c r="P12" t="str">
+        <v/>
+      </c>
+      <c r="Q12" t="str">
         <v>conv_5801kq9j2ptef53sdz089y7qarx1</v>
       </c>
-      <c r="R3" t="str" xml:space="preserve">
+      <c r="R12" t="str" xml:space="preserve">
         <v xml:space="preserve">Agent: Namaste 
 I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
 Would you be willing to hear a brief message about Maa Umiya and our mission?
@@ -589,59 +1166,59 @@
 Agent: જય મા ઉમિયા! મા ઉમિયા તમને અને તમારા પરિવારને સદા આશીર્વાદ આપે. શુભ દિવસ રહે...</v>
       </c>
     </row>
-    <row r="4" xml:space="preserve">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="str">
+    <row r="13" xml:space="preserve">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="str">
         <v>2026-04-28T08:08:49.302Z</v>
       </c>
-      <c r="C4" t="str">
-        <v/>
-      </c>
-      <c r="D4" t="str">
-        <v/>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4">
+      <c r="C13" t="str">
+        <v/>
+      </c>
+      <c r="D13" t="str">
+        <v/>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
         <v>5</v>
       </c>
-      <c r="I4" t="str">
+      <c r="I13" t="str">
         <v>Gujarati</v>
       </c>
-      <c r="J4" t="str">
+      <c r="J13" t="str">
         <v>gu</v>
       </c>
-      <c r="K4" t="str">
+      <c r="K13" t="str">
         <v>English, Gujarati</v>
       </c>
-      <c r="L4" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="M4" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="N4" t="str">
+      <c r="L13" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M13" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="N13" t="str">
         <v>unknown</v>
       </c>
-      <c r="O4" t="str">
+      <c r="O13" t="str">
         <v>ગુજરાતી.</v>
       </c>
-      <c r="P4" t="str">
-        <v/>
-      </c>
-      <c r="Q4" t="str">
+      <c r="P13" t="str">
+        <v/>
+      </c>
+      <c r="Q13" t="str">
         <v>conv_0601kq9j10aff04bte8ak7gpqqbx</v>
       </c>
-      <c r="R4" t="str" xml:space="preserve">
+      <c r="R13" t="str" xml:space="preserve">
         <v xml:space="preserve">Agent: Namaste 
 I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
 Would you be willing to hear a brief message about Maa Umiya and our mission?
@@ -654,59 +1231,59 @@
 Agent: ધન્યવાદ. મા ઉમિયા અને વિશ્વ ઉમિયા ફાઉન્ડેશન વિશે સંક્ષિપ્ત સમાચાર સાંભળવા તમારી સા...</v>
       </c>
     </row>
-    <row r="5" xml:space="preserve">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="str">
+    <row r="14" xml:space="preserve">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="str">
         <v>2026-04-28T08:04:48.175Z</v>
       </c>
-      <c r="C5" t="str">
-        <v/>
-      </c>
-      <c r="D5" t="str">
-        <v/>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
+      <c r="C14" t="str">
+        <v/>
+      </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
         <v>13</v>
       </c>
-      <c r="I5" t="str">
+      <c r="I14" t="str">
         <v>Hindi</v>
       </c>
-      <c r="J5" t="str">
+      <c r="J14" t="str">
         <v>hi</v>
       </c>
-      <c r="K5" t="str">
+      <c r="K14" t="str">
         <v>English, Gujarati, Hindi</v>
       </c>
-      <c r="L5" t="str">
+      <c r="L14" t="str">
         <v>Yes</v>
       </c>
-      <c r="M5" t="str">
+      <c r="M14" t="str">
         <v>Willing to join</v>
       </c>
-      <c r="N5" t="str">
+      <c r="N14" t="str">
         <v>willing_to_join</v>
       </c>
-      <c r="O5" t="str">
+      <c r="O14" t="str">
         <v>Okay. हाँ, मैं वही हूँ।</v>
       </c>
-      <c r="P5" t="str">
-        <v/>
-      </c>
-      <c r="Q5" t="str">
+      <c r="P14" t="str">
+        <v/>
+      </c>
+      <c r="Q14" t="str">
         <v>conv_9201kq9hsbc8egfs31f788amy56w</v>
       </c>
-      <c r="R5" t="str" xml:space="preserve">
+      <c r="R14" t="str" xml:space="preserve">
         <v xml:space="preserve">Agent: Namaste 
 I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
 Would you be willing to hear a brief message about Maa Umiya and our mission?
@@ -727,59 +1304,59 @@
 Agent: आपका स्वागत है।[grateful] माँ उमिया आपके और आपके परिवार के जीवन में शांति और सुख लाएं।[peaceful] आपका दिन शुभ हो।जय माँ उमिया 🙏</v>
       </c>
     </row>
-    <row r="6" xml:space="preserve">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="str">
+    <row r="15" xml:space="preserve">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="str">
         <v>2026-04-28T08:02:30.875Z</v>
       </c>
-      <c r="C6" t="str">
-        <v/>
-      </c>
-      <c r="D6" t="str">
-        <v/>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
+      <c r="C15" t="str">
+        <v/>
+      </c>
+      <c r="D15" t="str">
+        <v/>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
         <v>9</v>
       </c>
-      <c r="I6" t="str">
+      <c r="I15" t="str">
         <v>English</v>
       </c>
-      <c r="J6" t="str">
+      <c r="J15" t="str">
         <v>en</v>
       </c>
-      <c r="K6" t="str">
+      <c r="K15" t="str">
         <v>English, Gujarati, Hindi</v>
       </c>
-      <c r="L6" t="str">
+      <c r="L15" t="str">
         <v>Yes</v>
       </c>
-      <c r="M6" t="str">
+      <c r="M15" t="str">
         <v>Willing to join</v>
       </c>
-      <c r="N6" t="str">
+      <c r="N15" t="str">
         <v>willing_to_join</v>
       </c>
-      <c r="O6" t="str">
+      <c r="O15" t="str">
         <v>Okay. Sir.</v>
       </c>
-      <c r="P6" t="str">
-        <v/>
-      </c>
-      <c r="Q6" t="str">
+      <c r="P15" t="str">
+        <v/>
+      </c>
+      <c r="Q15" t="str">
         <v>conv_5901kq9hptgbe6rt4tjjqhnfmwk3</v>
       </c>
-      <c r="R6" t="str" xml:space="preserve">
+      <c r="R15" t="str" xml:space="preserve">
         <v xml:space="preserve">Agent: Namaste 
 I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
 Would you be ...
@@ -793,115 +1370,115 @@
 Agent: सारा, महोदय। क्या आप माँ उमिया और विश्व उमिया फाउंडेशन के बारे में एक संक्षिप्त संदेश सुनने के लिए तैयार हैं?</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="str">
+    <row r="16">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="str">
         <v>2026-04-28T06:42:54.419Z</v>
       </c>
-      <c r="C7" t="str">
-        <v/>
-      </c>
-      <c r="D7" t="str">
-        <v/>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7" t="str">
+      <c r="C16" t="str">
+        <v/>
+      </c>
+      <c r="D16" t="str">
+        <v/>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16" t="str">
         <v>English</v>
       </c>
-      <c r="J7" t="str">
+      <c r="J16" t="str">
         <v>en</v>
       </c>
-      <c r="K7" t="str">
+      <c r="K16" t="str">
         <v>English</v>
       </c>
-      <c r="L7" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="M7" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="N7" t="str">
+      <c r="L16" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M16" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="N16" t="str">
         <v>unknown</v>
       </c>
-      <c r="O7" t="str">
+      <c r="O16" t="str">
         <v>Transcript: Summary couldn't be generated for this call.</v>
       </c>
-      <c r="P7" t="str">
-        <v/>
-      </c>
-      <c r="Q7" t="str">
+      <c r="P16" t="str">
+        <v/>
+      </c>
+      <c r="Q16" t="str">
         <v>conv_7301kq9d735ve92stwtsszksq7v2</v>
       </c>
-      <c r="R7" t="str">
+      <c r="R16" t="str">
         <v>Transcript: Summary couldn't be generated for this call.</v>
       </c>
     </row>
-    <row r="8" xml:space="preserve">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="str">
+    <row r="17" xml:space="preserve">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="str">
         <v>2026-04-28T06:42:53.484Z</v>
       </c>
-      <c r="C8" t="str">
-        <v/>
-      </c>
-      <c r="D8" t="str">
-        <v/>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-      <c r="H8">
+      <c r="C17" t="str">
+        <v/>
+      </c>
+      <c r="D17" t="str">
+        <v/>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
         <v>9</v>
       </c>
-      <c r="I8" t="str">
+      <c r="I17" t="str">
         <v>Gujarati</v>
       </c>
-      <c r="J8" t="str">
+      <c r="J17" t="str">
         <v>gu</v>
       </c>
-      <c r="K8" t="str">
+      <c r="K17" t="str">
         <v>English, Gujarati</v>
       </c>
-      <c r="L8" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="M8" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="N8" t="str">
+      <c r="L17" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M17" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="N17" t="str">
         <v>unknown</v>
       </c>
-      <c r="O8" t="str">
+      <c r="O17" t="str">
         <v>હા</v>
       </c>
-      <c r="P8" t="str">
-        <v/>
-      </c>
-      <c r="Q8" t="str">
+      <c r="P17" t="str">
+        <v/>
+      </c>
+      <c r="Q17" t="str">
         <v>conv_9001kq9cx1bceky9cfvjzpq4tc09</v>
       </c>
-      <c r="R8" t="str" xml:space="preserve">
+      <c r="R17" t="str" xml:space="preserve">
         <v xml:space="preserve">Agent: Namaste 
 I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
 Would you be willing to hear a brief message about Maa Umiya and our mission?
@@ -918,62 +1495,62 @@
 Agent: ધન્યવાદ 🙏યુમિયા ધામ વિશ્વના સૌથી ઊંચા મંદિરોમાંના એક તરીકે વિકસાવવામાં આવી રહ્યું છે, જે આસ્થા, એકતા અને ભક્તિનું પ્રતીક છે.વિશ્વ ઉમિયા ફાઉન્ડેશન આધ્યાત્મિકતા, શિક્ષણ, સ્વાસ્...</v>
       </c>
     </row>
-    <row r="9" xml:space="preserve">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="str">
+    <row r="18" xml:space="preserve">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="str">
         <v>2026-04-28T06:31:37.032Z</v>
       </c>
-      <c r="C9" t="str">
-        <v/>
-      </c>
-      <c r="D9" t="str">
-        <v/>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-      <c r="H9">
-        <v>1</v>
-      </c>
-      <c r="I9" t="str">
+      <c r="C18" t="str">
+        <v/>
+      </c>
+      <c r="D18" t="str">
+        <v/>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18" t="str">
         <v>English</v>
       </c>
-      <c r="J9" t="str">
+      <c r="J18" t="str">
         <v>en</v>
       </c>
-      <c r="K9" t="str">
+      <c r="K18" t="str">
         <v>English</v>
       </c>
-      <c r="L9" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="M9" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="N9" t="str">
+      <c r="L18" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M18" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="N18" t="str">
         <v>unknown</v>
       </c>
-      <c r="O9" t="str" xml:space="preserve">
+      <c r="O18" t="str" xml:space="preserve">
         <v xml:space="preserve">Agent: Namaste 
 I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
 Would you be willing to hear a brief message about Maa Umiya and our mission?
 Umiya Dham is being develope</v>
       </c>
-      <c r="P9" t="str">
-        <v/>
-      </c>
-      <c r="Q9" t="str">
+      <c r="P18" t="str">
+        <v/>
+      </c>
+      <c r="Q18" t="str">
         <v>conv_8301kq9chf18f59barx86mgyqn9a</v>
       </c>
-      <c r="R9" t="str" xml:space="preserve">
+      <c r="R18" t="str" xml:space="preserve">
         <v xml:space="preserve">Agent: Namaste 
 I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
 Would you be willing to hear a brief message about Maa Umiya and our mission?
@@ -981,121 +1558,121 @@
 At Vishv Umiya Foundation, the mission is to uplift society through ...</v>
       </c>
     </row>
-    <row r="10" xml:space="preserve">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="str">
+    <row r="19" xml:space="preserve">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="str">
         <v>2026-04-28T06:30:38.685Z</v>
       </c>
-      <c r="C10" t="str">
-        <v/>
-      </c>
-      <c r="D10" t="str">
-        <v/>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-      <c r="H10">
-        <v>1</v>
-      </c>
-      <c r="I10" t="str">
+      <c r="C19" t="str">
+        <v/>
+      </c>
+      <c r="D19" t="str">
+        <v/>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19" t="str">
         <v>English</v>
       </c>
-      <c r="J10" t="str">
+      <c r="J19" t="str">
         <v>en</v>
       </c>
-      <c r="K10" t="str">
+      <c r="K19" t="str">
         <v>English</v>
       </c>
-      <c r="L10" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="M10" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="N10" t="str">
+      <c r="L19" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M19" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="N19" t="str">
         <v>unknown</v>
       </c>
-      <c r="O10" t="str" xml:space="preserve">
+      <c r="O19" t="str" xml:space="preserve">
         <v xml:space="preserve">Agent: Namaste 
 I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
 Would you be willing to hear a brief message about Maa Umiya and our mission?
 Umiya Dham is being develope</v>
       </c>
-      <c r="P10" t="str">
-        <v/>
-      </c>
-      <c r="Q10" t="str">
+      <c r="P19" t="str">
+        <v/>
+      </c>
+      <c r="Q19" t="str">
         <v>conv_6701kq9cg2eqer287bf4msmr1rhh</v>
       </c>
-      <c r="R10" t="str" xml:space="preserve">
+      <c r="R19" t="str" xml:space="preserve">
         <v xml:space="preserve">Agent: Namaste 
 I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
 Would you be willing to hear a brief message about Maa Umiya and our mission?
 Umiya Dham is being developed as one...</v>
       </c>
     </row>
-    <row r="11" xml:space="preserve">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="str">
+    <row r="20" xml:space="preserve">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="str">
         <v>2026-04-28T05:38:40.915Z</v>
       </c>
-      <c r="C11" t="str">
+      <c r="C20" t="str">
         <v>+919328481970</v>
       </c>
-      <c r="D11" t="str">
-        <v/>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-      <c r="H11">
+      <c r="D20" t="str">
+        <v/>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20">
         <v>19</v>
       </c>
-      <c r="I11" t="str">
+      <c r="I20" t="str">
         <v>Hindi</v>
       </c>
-      <c r="J11" t="str">
+      <c r="J20" t="str">
         <v>hi</v>
       </c>
-      <c r="K11" t="str">
+      <c r="K20" t="str">
         <v>English, Hindi, Gujarati</v>
       </c>
-      <c r="L11" t="str">
+      <c r="L20" t="str">
         <v>Yes</v>
       </c>
-      <c r="M11" t="str">
+      <c r="M20" t="str">
         <v>Willing to join</v>
       </c>
-      <c r="N11" t="str">
+      <c r="N20" t="str">
         <v>willing_to_join</v>
       </c>
-      <c r="O11" t="str">
+      <c r="O20" t="str">
         <v>Okay, thank you.</v>
       </c>
-      <c r="P11" t="str">
+      <c r="P20" t="str">
         <v>CAd3fa254243c464a1730f45c7c56505ed</v>
       </c>
-      <c r="Q11" t="str">
+      <c r="Q20" t="str">
         <v>conv_5701kq99de98eg794mxra8d73bwb</v>
       </c>
-      <c r="R11" t="str" xml:space="preserve">
+      <c r="R20" t="str" xml:space="preserve">
         <v xml:space="preserve">Agent: Namaste 
 I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
 Would you be willing to hear a brief message about Maa Umiya and our mission?
@@ -1122,59 +1699,59 @@
 Agent: ...</v>
       </c>
     </row>
-    <row r="12" xml:space="preserve">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="str">
+    <row r="21" xml:space="preserve">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="str">
         <v>2026-04-28T05:28:57.765Z</v>
       </c>
-      <c r="C12" t="str">
+      <c r="C21" t="str">
         <v>+919328481970</v>
       </c>
-      <c r="D12" t="str">
-        <v/>
-      </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-      <c r="H12">
+      <c r="D21" t="str">
+        <v/>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21">
         <v>15</v>
       </c>
-      <c r="I12" t="str">
+      <c r="I21" t="str">
         <v>Hindi</v>
       </c>
-      <c r="J12" t="str">
+      <c r="J21" t="str">
         <v>hi</v>
       </c>
-      <c r="K12" t="str">
+      <c r="K21" t="str">
         <v>English, Hindi</v>
       </c>
-      <c r="L12" t="str">
+      <c r="L21" t="str">
         <v>Yes</v>
       </c>
-      <c r="M12" t="str">
+      <c r="M21" t="str">
         <v>Willing to join</v>
       </c>
-      <c r="N12" t="str">
+      <c r="N21" t="str">
         <v>willing_to_join</v>
       </c>
-      <c r="O12" t="str">
+      <c r="O21" t="str">
         <v>Yes, जानना चाहूँगा।</v>
       </c>
-      <c r="P12" t="str">
+      <c r="P21" t="str">
         <v>CA34c672f4a33b63610704a7d7f3ade6ab</v>
       </c>
-      <c r="Q12" t="str">
+      <c r="Q21" t="str">
         <v>conv_8201kq98we89eh6v5hpy42ncxkfd</v>
       </c>
-      <c r="R12" t="str" xml:space="preserve">
+      <c r="R21" t="str" xml:space="preserve">
         <v xml:space="preserve">Agent: Namaste 
 I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
 Would you be willing to hear a brief message about Maa Umiya and our mission?
@@ -1198,7 +1775,7 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R21"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/call-qualifications.xlsx
+++ b/data/call-qualifications.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:R43"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -460,25 +460,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-28T10:09:01.826Z</v>
+        <v>2026-04-28T11:20:10.827Z</v>
       </c>
       <c r="C2" t="str">
-        <v/>
+        <v>+919328481970</v>
       </c>
       <c r="D2" t="str">
-        <v/>
+        <v>completed</v>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>+919328481970</v>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>+27872503011</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I2" t="str">
         <v>Gujarati</v>
@@ -487,27 +487,1440 @@
         <v>gu</v>
       </c>
       <c r="K2" t="str">
+        <v>English, Gujarati, Hindi</v>
+      </c>
+      <c r="L2" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M2" t="str">
+        <v>Willing to join</v>
+      </c>
+      <c r="N2" t="str">
+        <v>willing_to_join</v>
+      </c>
+      <c r="O2" t="str">
+        <v>Yeah, so my language, so my language is Gujarati.</v>
+      </c>
+      <c r="P2" t="str">
+        <v>CAe8810eabc8222e0ec296ea49b31e2279</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>conv_1601kq9x17zsfbmrr9c0fthc5f8a</v>
+      </c>
+      <c r="R2" t="str" xml:space="preserve">
+        <v xml:space="preserve">Agent: Namaste 🙏 Jai Maa Umiya I am calling from Vishv Umiya Foundation. 
+Before we...
+Prospect: કે બંધ કર દે તું.હા, બંધ કરી દે.બધી શબ્દ થઈ ગયું. આય ને, language choose કરો, પછી સમાધાન કરો. હું એને પૂછ્યું જ નહીં.હા.હા. હા. હા. હા
+Agent: [slow] કૃપા...
+Prospect: Hindi.
+Agent: बहुत अच्छा, हम...
+Prospect: Yeah, so my language, so my language is Gujarati.
+Agent: [slow] ખૂબ સરસ, આપણે ગુજરાતીમાં વાત કરીશું. 🙏 [slow] શું આપ માઁ ઉમિયા અને વિશ્વ ઉમિયા ફાઉન્ડેશન...
+Prospect: હા.હમ્મ.
+Agent: ...
+Prospect: અને તમે કેવી રીતે કરો છો?તમે કેવી રીતે કરો છો?
+Agent: ...
+Prospect: બરાબર.બરાબર.
+Agent: [slow] ઉમિયા ધામ વિશ્વના સૌથી ઊંચા મંદિરોમાંનું એક બની રહ્યું છે — જે માઁ ઉ...</v>
+      </c>
+    </row>
+    <row r="3" xml:space="preserve">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-04-28T11:17:52.294Z</v>
+      </c>
+      <c r="C3" t="str">
+        <v>+0170247</v>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3" t="str">
+        <v>English</v>
+      </c>
+      <c r="J3" t="str">
+        <v>en</v>
+      </c>
+      <c r="K3" t="str">
+        <v>English</v>
+      </c>
+      <c r="L3" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M3" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="N3" t="str">
+        <v>unknown</v>
+      </c>
+      <c r="O3" t="str" xml:space="preserve">
+        <v xml:space="preserve">Agent: Namaste 🙏 Jai Maa Umiya I am calling from Vishv Umiya Foundation. 
+Before we begin, which language are you most comfortable speaking — English, Hindi, or Gujarati?</v>
+      </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
+      <c r="Q3" t="str">
+        <v>conv_5001kq9wye78epgbaw3frd104fre</v>
+      </c>
+      <c r="R3" t="str" xml:space="preserve">
+        <v xml:space="preserve">Agent: Namaste 🙏 Jai Maa Umiya I am calling from Vishv Umiya Foundation. 
+Before we begin, which language are you most comfortable speaking — English, Hindi, or Gujarati?</v>
+      </c>
+    </row>
+    <row r="4" xml:space="preserve">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-04-28T11:16:54.997Z</v>
+      </c>
+      <c r="C4" t="str">
+        <v>+0170247</v>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>5</v>
+      </c>
+      <c r="I4" t="str">
+        <v>Hindi</v>
+      </c>
+      <c r="J4" t="str">
+        <v>hi</v>
+      </c>
+      <c r="K4" t="str">
+        <v>Gujarati, English, Hindi</v>
+      </c>
+      <c r="L4" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M4" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="N4" t="str">
+        <v>unknown</v>
+      </c>
+      <c r="O4" t="str">
+        <v>नहीं।</v>
+      </c>
+      <c r="P4" t="str">
+        <v/>
+      </c>
+      <c r="Q4" t="str">
+        <v>conv_8801kq9wvgewektbwgarwwhczzfs</v>
+      </c>
+      <c r="R4" t="str" xml:space="preserve">
+        <v xml:space="preserve">Agent: Namaste 🙏 I am calling from Vishv Umiya Foundation. 
+Before we begin, which language are you most comfortable speaking — English, Hindi, or Gujarati?
+કયી ભાષામાં વાત કરવી ગમશે — English, Hindi, કે Gujarati?
+Prospect: Hindi.
+Agent: बहुत अच्छा, हम हिंदी में बात करेंगे। 🙏 क्या आप माँ उमिया और विश्व उमिया फाउंडेशन के बारे में एक छोटा सा संदेश सुनना चाहेंगे?
+Prospect: नहीं।
+Agent: विश्व उमिया फाउंडेशन से जुड़ने के लिए धन्यवाद। माँ उमिया आपको और आपके परिवार को आशीर्वाद दें। आपका दिन शुभ हो। जय माँ उमिया। 🙏</v>
+      </c>
+    </row>
+    <row r="5" xml:space="preserve">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-04-28T11:15:26.059Z</v>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>7</v>
+      </c>
+      <c r="I5" t="str">
+        <v>English</v>
+      </c>
+      <c r="J5" t="str">
+        <v>en</v>
+      </c>
+      <c r="K5" t="str">
+        <v>Gujarati, English</v>
+      </c>
+      <c r="L5" t="str">
+        <v>No</v>
+      </c>
+      <c r="M5" t="str">
+        <v>Not willing to join</v>
+      </c>
+      <c r="N5" t="str">
+        <v>not_willing_to_join</v>
+      </c>
+      <c r="O5" t="str">
+        <v>No.</v>
+      </c>
+      <c r="P5" t="str">
+        <v/>
+      </c>
+      <c r="Q5" t="str">
+        <v>conv_2501kq9wrss2erk8fyhpx4fn6x8f</v>
+      </c>
+      <c r="R5" t="str" xml:space="preserve">
+        <v xml:space="preserve">Agent: Namaste 🙏 I am calling from Vishv Umiya Foundation. 
+Before we begin, which language are you most comfortable speaking — English, Hindi, or Gujarati?
+કયી ભાષામાં વાત...
+Prospect: English.
+Agent: [happy] Wonderful, we'll continue in English. 🙏
+Would you be willing to hear a brief message about Maa Umiya and Vishv Umiya Foundation?
+Prospect: No.
+Agent: [sad] Thank you for connecting with Vishv Umiya Foundation. May Maa Umiya bless you and your family. Have a peaceful day. Jai Maa Umiya. 🙏
+Prospect: Thank you.
+Agent: [happy] You're most welcome. Jai Maa Umiya. 🙏</v>
+      </c>
+    </row>
+    <row r="6" xml:space="preserve">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-04-28T11:07:54.481Z</v>
+      </c>
+      <c r="C6" t="str">
+        <v>+919328481970</v>
+      </c>
+      <c r="D6" t="str">
+        <v/>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>7</v>
+      </c>
+      <c r="I6" t="str">
+        <v>Hindi</v>
+      </c>
+      <c r="J6" t="str">
+        <v>hi</v>
+      </c>
+      <c r="K6" t="str">
+        <v>Gujarati, English, Hindi</v>
+      </c>
+      <c r="L6" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M6" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="N6" t="str">
+        <v>unknown</v>
+      </c>
+      <c r="O6" t="str">
+        <v>अ, टीम से जोड़ दीजिए।</v>
+      </c>
+      <c r="P6" t="str">
+        <v>CA1dfbb77a3425e6c8adce255bbd4089fb</v>
+      </c>
+      <c r="Q6" t="str">
+        <v>conv_5201kq9w9x6wfzdbj53bnc6qz3rp</v>
+      </c>
+      <c r="R6" t="str" xml:space="preserve">
+        <v xml:space="preserve">Agent: Namaste 🙏 I am calling from Vishv Umiya Foundation. 
+Before we begin, which language are you most comfortable speaking — English, Hindi, or Gujarati?
+કયી ભાષામાં...
+Prospect: Hindi.
+Agent: बहुत अच्छा, हम हिंदी में बात करेंगे। [happy] 🙏
+क्या आप माँ उमिया और विश्व उमिया फाउंडेशन के बारे में एक छोटा सा संदेश सुनना चाहेंगे?
+Prospect: जी।
+Agent: उमिया धाम विश्व के सबसे ऊँचे मंदिरों में से एक के रूप में विकसित हो रहा है — जो माँ उमिया के प्रति आस्था, एकता और भक्ति का प्रतीक है। विश्व उमिया फाउंडेशन आध्यात्मिकता, शिक्षा, स्वास्थ्य सेवा और सामाजिक उत्थान के माध्यम से समाज की सेवा करता है।
+क्या आप और जानना चाहेंगे, या मैं आपको हमारी टीम से जोड़ूँ?
+Prospect: अ, टीम से जोड़ दीजिए।
+Agent: [happy] बहुत अच्छा, मैं हमारी टीम को आपसे संपर्क करने की व्यवस्था करूँगा। 🙏
+विश्व उमिया फाउंडेशन से जुड़ने के लिए धन्यवाद। माँ उमिया आपको और आपके परिवार को आशीर्वाद दें। आपका दिन शुभ हो। जय माँ उमिया। 🙏</v>
+      </c>
+    </row>
+    <row r="7" xml:space="preserve">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-04-28T10:59:16.465Z</v>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>10</v>
+      </c>
+      <c r="I7" t="str">
+        <v>Gujarati</v>
+      </c>
+      <c r="J7" t="str">
+        <v>gu</v>
+      </c>
+      <c r="K7" t="str">
         <v>English, Gujarati</v>
       </c>
-      <c r="L2" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="M2" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="N2" t="str">
+      <c r="L7" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M7" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="N7" t="str">
         <v>unknown</v>
       </c>
-      <c r="O2" t="str">
+      <c r="O7" t="str">
+        <v>તમારો હોય.</v>
+      </c>
+      <c r="P7" t="str">
+        <v/>
+      </c>
+      <c r="Q7" t="str">
+        <v>conv_1801kq9vs5yqekbtjqek7xbbcfbn</v>
+      </c>
+      <c r="R7" t="str" xml:space="preserve">
+        <v xml:space="preserve">Agent: Namaste! I am calling on behalf of Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
+Prospect: Gujarati.
+Agent: ખૂબ સારું! હું ગુજરાતીમાં વાત કરીશ।
+Prospect: આગળ બોલો. પ્રતિક બોલો.
+Agent: ઉમિયા ધામ વિશ્વના સૌથી ઊંચા મંદિરોમાંથી એક તરીકે વિકસાવવામાં આવી રહ્યું છે, જે શક્તિ, ભક્તિ અને સાંસ્કૃતિક ગૌરવનું પ્રતીક છે અને એકતા તથા આધ્યાત્મિકતાનો સંદેશ ફેલાવે છે. વિશ્વ ઉમિયા ફાઉન્ડેશનનું મિશન છે આધ્યાત્મિકતા, શિક્ષણ, આરોગ્ય અને સમાજ સેવા દ્વારા સમાજને ઉન્નત કરવું અને સૌ માટે એક ઉજ્જવળ ભવિષ્ય બનાવવું. વિશ્વ ઉમિયા ફાઉન્ડેશન અમદાવાદ સ્થિત એક બિન-નફાકારક સંસ્થા છે, જે માઁ ઉમિયાના આશીર્વાદથી માનવતાની સેવા માટે સમર્પિત છે.શું તમે વધુ જાણવા, અમારી વેબસાઇટ જોવા, અથવા અમારી ટીમ સાથે જોડાવા ઇચ્છો છો?
+Prospect: ના, નથી જોડાવા માગતા.
+Agent: તમારા સમય માટે આભાર. માઁ ઉમિયા તમને અને તમારા પરિવારને સદા આશીર્વાદ આપે. જય માઁ ઉમિયા...
+Prospect: તમને પણ.
+Agent: ધન્યવાદ, માઁ ઉમિયાની કૃપા હંમેશા તમને સાથે રહે. શુભ દિવસ હોય.
+Prospect: તમારો હોય.</v>
+      </c>
+    </row>
+    <row r="8" xml:space="preserve">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-04-28T10:57:12.991Z</v>
+      </c>
+      <c r="C8" t="str">
+        <v/>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>11</v>
+      </c>
+      <c r="I8" t="str">
+        <v>Gujarati</v>
+      </c>
+      <c r="J8" t="str">
+        <v>gu</v>
+      </c>
+      <c r="K8" t="str">
+        <v>English, Gujarati</v>
+      </c>
+      <c r="L8" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M8" t="str">
+        <v>Willing to join</v>
+      </c>
+      <c r="N8" t="str">
+        <v>willing_to_join</v>
+      </c>
+      <c r="O8" t="str">
+        <v>Okay.</v>
+      </c>
+      <c r="P8" t="str">
+        <v/>
+      </c>
+      <c r="Q8" t="str">
+        <v>conv_2601kq9vndzyf79tbm9c4g32z9h7</v>
+      </c>
+      <c r="R8" t="str" xml:space="preserve">
+        <v xml:space="preserve">Agent: Namaste 
+I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
+Would you be willing to hear a brief message about Maa Umiya and our mission?
+Umiya Dham is being developed as one of the tallest temples in the world, symbolizing strength, devotion, and cultural pride, and spreading a message of unity and spirituality.
+At Vishv Umiya Foundation, the...
+Prospect: ગુજરાતી.ગુજરાતી.
+Agent: ...
+Prospect: Then what?
+Agent: ...
+Prospect: Okay.
+Agent: સારું, ધન્યવાદ.અમે વિશ્વ ઉમિયા ફાઉન્ડેશન દ્વારા આધ્યાત્મિકતા, શિક્ષણ, સ્વાસ્થ્ય અને સમાજની ઉન્નતિ માટે કામ કરીએ છીએ.ઊમિયા ધામ વિશ્વના સૌથી ઊંચા મંદિરોમાંનું એક બની રહ્યું છે, જે આસ્થા, એકતા અને ભક્તિનું પ્રતીક છે.કેમ કે તમે વધુ જાણવા માંગો છો કે અમારી ટીમ સાથે સંપર્ક કરવો છે?
+Prospect: સંપર્ક કરવો છે.
+Agent: સરસ! મને ખુશી છે કે તમે અમારી ટીમ સાથે સંપર્ક કરવા માંગો છો.મેં તમને અમારી ટીમ સાથે જોડી દીધા છું.અમારી વેબસાઇટ પર પણ વધુ માહિતી મેળવી શકો છો: https://www.vuf...
+Prospect: જય માં મોં, જય માં મોં. કમ દીધું હોય?હા, હા, હા. હા
+Agent: [excited] જય માં મોં! જય માં મોં! આપની ભક્તિ અને સાથે માં આનંદ છે...</v>
+      </c>
+    </row>
+    <row r="9" xml:space="preserve">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-04-28T10:55:23.244Z</v>
+      </c>
+      <c r="C9" t="str">
+        <v/>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>19</v>
+      </c>
+      <c r="I9" t="str">
+        <v>Gujarati</v>
+      </c>
+      <c r="J9" t="str">
+        <v>gu</v>
+      </c>
+      <c r="K9" t="str">
+        <v>English, Gujarati</v>
+      </c>
+      <c r="L9" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M9" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="N9" t="str">
+        <v>unknown</v>
+      </c>
+      <c r="O9" t="str">
+        <v>અરે, સાચી કહેવાની વાત છે.હા.</v>
+      </c>
+      <c r="P9" t="str">
+        <v/>
+      </c>
+      <c r="Q9" t="str">
+        <v>conv_5701kq9vht7yfwg9sazq12kfy8vc</v>
+      </c>
+      <c r="R9" t="str" xml:space="preserve">
+        <v xml:space="preserve">Agent: Namaste 
+I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or...
+Prospect: હા, તો બે.
+Agent: ...
+Prospect: ગુજરાતી.
+Agent: ...
+Prospect: ગુજરાતી.
+Agent: સારું, હું ગુજરાતીમાં વાત કરીશ.કૃપા કરીને જણાવો કે કેમ મા ઉમિયા અને વિશ્વ ઉમિયા ફાઉન્ડેશન વિશે સંક્ષિપ્ત સમાચાર સાંભળવા માંગો છો?
+Prospect: શું તમું કહારે મેરે કો? એ તો મેરે કો તમુ�ં કહારે? સાંભળવા માંગો છો?
+Agent: [slow] હા, મા ઉમિયા અને વિશ્વ ઉમિયા ફાઉન્ડેશન વિશે સંક્ષિપ્ત માહિતી સાંભળવા માંગો છો?
+Prospect: હા, સાંભળવા માંગીએ છીએ.
+Agent: [happy] આભાર, મા ઉમિયા અને વિશ્વ ઉમિયા ફાઉન્ડેશન વિશે સંક્ષિપ્ત માહિતી આપું છું.યુમિયા ધામ વિશ્વના સૌથી ઊંચા મંદિરોમાંનું એક તરીકે વિકસાવવામાં આવી રહ્યું છે, જે ભક્તિ, એકતા અને આધ્યાત્મિકતાનું પ્રતીક છે.વિશ્વ ઉમિયા ફાઉન્ડેશન આધ્યાત્મિકતા, શિક્ષણ, સ્વાસ્થ્ય અને સમુદાયની ઉન્નતિ દ્વારા સમાજની સેવા કરે છે.કેમ કે વધુ માહિતી માટે જોડાવા માંગો છો કે અમારી ટીમ સાથે સંપર્ક કરવા માંગો છો?
+Prospect: હા, સંપર્ક કરવા માંગીએ છીએ.કોનું? કોનું?
+Agent: [excited] સરસ! હું તમને અમારી ટીમ સાથે જોડીશ.કૃપા કરીને થોડી વાર રાહ જુઓ.
+Prospect: હમ્મ, વારા જોઉં છું.હમ્મ, હમ્મ, હમ્મ.
+Agent: [calm] હા, થોડી વાર રાહ જુઓ. અમારી ટીમ તમને જોડી રહી છે. શાંત રહો, સારું થશે.
+Prospect: પણ એ તમે કહો ને કે હું તમને કેવી રીતે કહીશ? �તમે તો બોલો ને કે હું તમને કેવી
+Agent: ...
+Prospect: અરે, સાચી કહેવાની વાત છે.હા.
+Agent: [calm] હા, હું સમજું છું...</v>
+      </c>
+    </row>
+    <row r="10" xml:space="preserve">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-04-28T10:53:21.856Z</v>
+      </c>
+      <c r="C10" t="str">
+        <v>+0170247</v>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10" t="str">
+        <v>English</v>
+      </c>
+      <c r="J10" t="str">
+        <v>en</v>
+      </c>
+      <c r="K10" t="str">
+        <v>English</v>
+      </c>
+      <c r="L10" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M10" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="N10" t="str">
+        <v>unknown</v>
+      </c>
+      <c r="O10" t="str" xml:space="preserve">
+        <v xml:space="preserve">Agent: Namaste 
+I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
+Would you be willing to hear a brief message about Maa Umiya and our mission?
+Umiya Dham is being develope</v>
+      </c>
+      <c r="P10" t="str">
+        <v/>
+      </c>
+      <c r="Q10" t="str">
+        <v>conv_9901kq9vh6njeezb5nrh2nmtfak0</v>
+      </c>
+      <c r="R10" t="str" xml:space="preserve">
+        <v xml:space="preserve">Agent: Namaste 
+I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
+Would you be willing to hear a brief message about Maa Umiya and our mission?
+Umiya Dham is being developed as one of the tallest temples in the world, symbolizing strength, devotion, and cultural pride, and spreading a message of unity and spirituality.
+At Vishv Umiya Foundation, the mission is to uplift society through spirituality, education, healthcare, and community service, creating a better and brighter future for all.
+"Thank you for connecting with Vishv Umiya Foundation. We truly value your time. May Maa Umiya bless you and your family. Have a wonderful day."</v>
+      </c>
+    </row>
+    <row r="11" xml:space="preserve">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-04-28T10:53:00.654Z</v>
+      </c>
+      <c r="C11" t="str">
+        <v/>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>15</v>
+      </c>
+      <c r="I11" t="str">
+        <v>English</v>
+      </c>
+      <c r="J11" t="str">
+        <v>en</v>
+      </c>
+      <c r="K11" t="str">
+        <v>English, Gujarati, Hindi</v>
+      </c>
+      <c r="L11" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M11" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="N11" t="str">
+        <v>unknown</v>
+      </c>
+      <c r="O11" t="str">
+        <v>...</v>
+      </c>
+      <c r="P11" t="str">
+        <v/>
+      </c>
+      <c r="Q11" t="str">
+        <v>conv_5101kq9ve6jkfpctaqyrm7cptwfw</v>
+      </c>
+      <c r="R11" t="str" xml:space="preserve">
+        <v xml:space="preserve">Agent: Namaste! I am calling on behalf of Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
+Prospect: Gujarati.
+Agent: ખૂબ સારું! હું ગુજરાતીમાં વાત કરીશ।
+Prospect: ...
+Agent: માફ કરજો, કૃપા કરીને મને જણાવો કે તમે કયું ભાષા પસંદ કરો છો? હું તમને ગુજરાતીમાં વાત કરીશ.
+Prospect: Gujarati.
+Agent: ખૂબ સારું! હું ગુજરાતીમાં વાત કરીશ।
+Prospect: Sab aara hai, bhai.
+Agent: ખૂબ સારું, ભાઈ! હું તમને વિશ્વ ઉમિયા ફાઉન્ડેશન અને ઉમિયા ધામ વિશે જણાવીશ.
+Prospect: ...
+Agent: માફ કરજો, કૃપા કરીને મને જણાવો કે તમે વધુ જાણવા ઇચ્છો છો કે નહીં?
+Prospect: Hindi.
+Agent: बहुत अच्छा! मैं हिंदी में बात करूँगा।
+Prospect: ...
+Agent: माफ कीजिए, कृपया मुझे बताएं कि आप अधिक जानकारी चाहते हैं या फिर हमारी वेबसाइट देखना चाहेंगे?</v>
+      </c>
+    </row>
+    <row r="12" xml:space="preserve">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-04-28T10:50:49.990Z</v>
+      </c>
+      <c r="C12" t="str">
+        <v/>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>9</v>
+      </c>
+      <c r="I12" t="str">
+        <v>Gujarati</v>
+      </c>
+      <c r="J12" t="str">
+        <v>gu</v>
+      </c>
+      <c r="K12" t="str">
+        <v>English, Gujarati</v>
+      </c>
+      <c r="L12" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M12" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="N12" t="str">
+        <v>unknown</v>
+      </c>
+      <c r="O12" t="str">
+        <v>હા, તમારી team સાથે સંપર્ક કરવો છે.</v>
+      </c>
+      <c r="P12" t="str">
+        <v/>
+      </c>
+      <c r="Q12" t="str">
+        <v>conv_8601kq9va8k5er3rzqm5zh194e8t</v>
+      </c>
+      <c r="R12" t="str" xml:space="preserve">
+        <v xml:space="preserve">Agent: Namaste 
+I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
+Would you be willing to hear a brief ...
+Prospect: કુછ આદિ.
+Agent: [slow] હા, માફ કરશો... કૃપા કરીને કહો કે તમે કયા ભાષામાં વાત કરવામાં આરામદાયક માનો છો? ઇંગ્લિશ, હિન્દી કે ગુજરાતી?
+Prospect: ગુજરાતી.
+Agent: [slow] ધન્યવાદ, માફ કરશો... કૃપા કરીને કહો કે તમે મા ઉમિયા અને વિશ્વ ઉમિયા ફાઉન્ડેશન વિશે સંક્ષિપ્ત માહિતી સાંભળવા માંગો છો?
+Prospect: હા.
+Agent: [happy] ધન્યવાદ તમારી સહભાગિતા માટે.યુમિયા ધામ વિશ્વના સૌથી ઊંચા મંદિરો પૈકી એક તરીકે વિકસાવવામાં આવી રહ્યું છે, જે ભક્તિ, એકતા અને આધ્યાત્મિકતાનું પ્રતીક છે.વિશ્વ ઉમિયા ફાઉન્ડેશન આધ્યાત્મિકતા, શિક્ષણ, સ્વાસ્થ્ય અને સમુદાયની ઉન્નતિ દ્વારા સમાજની સેવા કરે છે.કૃપા કરીને કહો, કે તમને વધુ માહિતી જોઈએ કે અમારી ટીમ સાથે સંપર્ક કરવો છે?
+Prospect: હા, તમારી team સાથે સંપર્ક કરવો છે.
+Agent: [excited] સરસ! મને ખુશી છે કે તમે અમારી ટીમ સાથે સંપર્ક કરવા માંગો છો. હું તમને સંપર્ક કરવા માટે તૈયાર છું. કૃપા કરીને થોડી વાર રાહ જુઓ.</v>
+      </c>
+    </row>
+    <row r="13" xml:space="preserve">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-04-28T10:47:53.449Z</v>
+      </c>
+      <c r="C13" t="str">
+        <v>+0170247</v>
+      </c>
+      <c r="D13" t="str">
+        <v/>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>8</v>
+      </c>
+      <c r="I13" t="str">
+        <v>English</v>
+      </c>
+      <c r="J13" t="str">
+        <v>en</v>
+      </c>
+      <c r="K13" t="str">
+        <v>English, Gujarati</v>
+      </c>
+      <c r="L13" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M13" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="N13" t="str">
+        <v>unknown</v>
+      </c>
+      <c r="O13" t="str">
+        <v>અમારે તો એની જરૂર નથી.અમારે આપણી જે system હોય ને એને check કરીએ ને.હમ્મ. હા, હ�</v>
+      </c>
+      <c r="P13" t="str">
+        <v/>
+      </c>
+      <c r="Q13" t="str">
+        <v>conv_2301kq9v688yfjntj76gv29txp48</v>
+      </c>
+      <c r="R13" t="str" xml:space="preserve">
+        <v xml:space="preserve">Agent: Namaste! I am calling on behalf of Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
+Prospect: Gujarati.
+Agent: ખૂબ સારું! હું ગુજરાતીમાં વાત કરીશ।
+Prospect: Hello?
+Agent: હા, હા માને છે. ...
+Prospect: Hello?
+Agent: હા, હા, હું છું...
+Prospect: અમારે તો એની જરૂર નથી.અમારે આપણી જે system હોય ને એને check કરીએ ને.હમ્મ. હા, હ�</v>
+      </c>
+    </row>
+    <row r="14" xml:space="preserve">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-04-28T10:46:46.503Z</v>
+      </c>
+      <c r="C14" t="str">
+        <v>+0170247</v>
+      </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>9</v>
+      </c>
+      <c r="I14" t="str">
+        <v>Gujarati</v>
+      </c>
+      <c r="J14" t="str">
+        <v>gu</v>
+      </c>
+      <c r="K14" t="str">
+        <v>Gujarati, English</v>
+      </c>
+      <c r="L14" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M14" t="str">
+        <v>Willing to join</v>
+      </c>
+      <c r="N14" t="str">
+        <v>willing_to_join</v>
+      </c>
+      <c r="O14" t="str">
+        <v>Yes.</v>
+      </c>
+      <c r="P14" t="str">
+        <v/>
+      </c>
+      <c r="Q14" t="str">
+        <v>conv_7201kq9v3kzzf4ssgvxthpy1cszs</v>
+      </c>
+      <c r="R14" t="str" xml:space="preserve">
+        <v xml:space="preserve">Agent: Namaste 🙏 I am calling from Vishv Umiya Foundation. 
+Before we begin, which language are you most comfortable speaking — English, Hindi, or Gujarati?
+કયી...
+Prospect: Gujarati.ગુજરાતી.
+Agent: [happy] ખૂબ સરસ, આપણે ગુજરાતીમાં વાત કરીશું. 🙏
+શું આપ માઁ ઉમિયા અને વિશ્વ ઉમિયા ફાઉન્ડેશન વિશે થોડી વાત સાંભળવા તૈયાર છો?
+Prospect: ...
+Agent: શું આપ માઁ ઉમિયા અને વિશ્વ ઉમિયા ફાઉન્ડેશન વિશે થોડી વાત સાંભળવા તૈયાર છો?
+Prospect: Yes.
+Agent: ઉમિયા ધામ વિશ્વના સૌથી ઊંચા મંદિરોમાંનું એક બની રહ્યું છે — જે માઁ ઉમિયા પ્રત્યેની શ્રદ્ધા, એકતા અને ભક્તિનું પ્રતીક છે. વિશ્વ ઉમિયા ફાઉન્ડેશન આધ્યાત્મિકતા, શિક્ષણ, આરોગ્ય સેવા અને સામાજિક...
+Prospect: Hello,જોડું?
+Agent: [happy] વિશ્વ ઉમિયા ફાઉન્ડેશન આધ્યાત્મિકતા, શિક્ષણ, આરોગ્ય સેવા અને સામાજિક ઉત્થાન દ્વારા સમાજની સેવા કરે છે.
+શું આપ વધુ જાણવા માંગો છો, અથવા હું આપને અમારી ટીમ સાથે જોડું?</v>
+      </c>
+    </row>
+    <row r="15" xml:space="preserve">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-04-28T10:45:40.864Z</v>
+      </c>
+      <c r="C15" t="str">
+        <v/>
+      </c>
+      <c r="D15" t="str">
+        <v/>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>3</v>
+      </c>
+      <c r="I15" t="str">
+        <v>English</v>
+      </c>
+      <c r="J15" t="str">
+        <v>en</v>
+      </c>
+      <c r="K15" t="str">
+        <v>English, Hindi</v>
+      </c>
+      <c r="L15" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M15" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="N15" t="str">
+        <v>unknown</v>
+      </c>
+      <c r="O15" t="str">
+        <v>Hindi.</v>
+      </c>
+      <c r="P15" t="str">
+        <v/>
+      </c>
+      <c r="Q15" t="str">
+        <v>conv_8301kq9v1txbfm1sf4zt3b6q56c0</v>
+      </c>
+      <c r="R15" t="str" xml:space="preserve">
+        <v xml:space="preserve">Agent: Namaste! I am calling on behalf of Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
+Prospect: Hindi.
+Agent: बहुत अच्छा! मैं हिंदी में बात करूँगा।उमिया धाम विश्व के सबसे ऊँचे मंदिरों में से एक के रूप में विकसित किया जा रहा है, जो शक्ति, भक्ति और सांस्कृतिक गौरव का प्रतीक है और एकता व आध्यात्मिकता का संदेश फैला रहा है। विश्व उमिया फाउंडेशन का मिशन है आध्यात्मिकता, शिक्षा, स्वास्थ्य और समाज सेवा के माध्यम से समाज को ऊपर उठाना और सबके लिए एक बेहतर भविष्य बनाना। विश्व उमिया फाउंडेशन अहमदाबाद स्थित एक गैर-लाभकारी संस्था है, जो माँ उमिया के आशीर्वाद से मानवता की सेवा के लिए समर्पित है।क्या आप और जानना चाहेंगे, हमारी वेबसाइट देखना चाहेंगे, या...</v>
+      </c>
+    </row>
+    <row r="16" xml:space="preserve">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-04-28T10:44:56.398Z</v>
+      </c>
+      <c r="C16" t="str">
+        <v>+0170247</v>
+      </c>
+      <c r="D16" t="str">
+        <v/>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>9</v>
+      </c>
+      <c r="I16" t="str">
+        <v>Gujarati</v>
+      </c>
+      <c r="J16" t="str">
+        <v>gu</v>
+      </c>
+      <c r="K16" t="str">
+        <v>Gujarati, English</v>
+      </c>
+      <c r="L16" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M16" t="str">
+        <v>Willing to join</v>
+      </c>
+      <c r="N16" t="str">
+        <v>willing_to_join</v>
+      </c>
+      <c r="O16" t="str">
+        <v>Yes.</v>
+      </c>
+      <c r="P16" t="str">
+        <v/>
+      </c>
+      <c r="Q16" t="str">
+        <v>conv_8601kq9tzqt8f7db3p2gkzfny331</v>
+      </c>
+      <c r="R16" t="str" xml:space="preserve">
+        <v xml:space="preserve">Agent: Namaste 🙏 I am calling from Vishv Umiya Foundation. 
+Before we begin, which language are you most comfortable speaking — English, Hindi, or Gujarati?
+કયી ભાષામાં વાત કરવી ગમશે — English, Hindi, કે Gujarati?
+Prospect: Gujarati.ગુજરાતી.
+Agent: ખૂબ સરસ, આપણે ગુજરાતીમાં વાત કરીશું. 🙏
+Prospect: Okay.
+Agent: શું આપ માઁ ઉમિયા અને વિશ્વ ઉમિયા ફાઉન્ડેશન વિશે થોડી વાત સાંભળવા તૈયાર છો?
+Prospect: ...
+Agent: I'm...
+Prospect: Yes.
+Agent: ખૂબ સરસ, આપણે આગળ વધીએ.ઉમિયા ધામ વિશ્વના સૌથી ઊંચા મંદિરોમાંનું એક બની રહ્યું છે — જે માઁ ઉમિયા પ્રત્યેની શ્રદ્ધા, એકતા અને ભક્તિનું પ્રતીક છે.વિશ્વ ઉમિયા ફાઉન્ડેશન આધ્યાત્મિકતા, શિક્ષણ, આરોગ્ય સેવા અને સામાજિક ઉત્થાન દ્વારા સમાજની સેવા કરે છે.કેમ કે આપ વધુ જાણવા માંગો છો, કે હું આપને અમારી ટ...</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-04-28T10:41:13.433Z</v>
+      </c>
+      <c r="C17" t="str">
+        <v/>
+      </c>
+      <c r="D17" t="str">
+        <v/>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17" t="str">
+        <v>English</v>
+      </c>
+      <c r="J17" t="str">
+        <v>en</v>
+      </c>
+      <c r="K17" t="str">
+        <v>English</v>
+      </c>
+      <c r="L17" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M17" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="N17" t="str">
+        <v>unknown</v>
+      </c>
+      <c r="O17" t="str">
+        <v>Agent: ...</v>
+      </c>
+      <c r="P17" t="str">
+        <v/>
+      </c>
+      <c r="Q17" t="str">
+        <v>conv_2201kq9tv6s4edv8x0mxn56dc2pj</v>
+      </c>
+      <c r="R17" t="str">
+        <v>Agent: ...</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2026-04-28T10:40:04.330Z</v>
+      </c>
+      <c r="C18" t="str">
+        <v/>
+      </c>
+      <c r="D18" t="str">
+        <v/>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18" t="str">
+        <v>English</v>
+      </c>
+      <c r="J18" t="str">
+        <v>en</v>
+      </c>
+      <c r="K18" t="str">
+        <v>English</v>
+      </c>
+      <c r="L18" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M18" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="N18" t="str">
+        <v>unknown</v>
+      </c>
+      <c r="O18" t="str">
+        <v>Agent: Namaste! I am calling on behalf of Vishv...</v>
+      </c>
+      <c r="P18" t="str">
+        <v/>
+      </c>
+      <c r="Q18" t="str">
+        <v>conv_6101kq9ts2r4f83tmt85ybqx9v1n</v>
+      </c>
+      <c r="R18" t="str">
+        <v>Agent: Namaste! I am calling on behalf of Vishv...</v>
+      </c>
+    </row>
+    <row r="19" xml:space="preserve">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2026-04-28T10:34:59.657Z</v>
+      </c>
+      <c r="C19" t="str">
+        <v/>
+      </c>
+      <c r="D19" t="str">
+        <v/>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19">
+        <v>5</v>
+      </c>
+      <c r="I19" t="str">
+        <v>Gujarati</v>
+      </c>
+      <c r="J19" t="str">
+        <v>gu</v>
+      </c>
+      <c r="K19" t="str">
+        <v>English, Gujarati</v>
+      </c>
+      <c r="L19" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M19" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="N19" t="str">
+        <v>unknown</v>
+      </c>
+      <c r="O19" t="str">
+        <v>હા, હું તમારી team સાથે જોડાવા ઇચ્છું છું.</v>
+      </c>
+      <c r="P19" t="str">
+        <v/>
+      </c>
+      <c r="Q19" t="str">
+        <v>conv_0301kq9tdxh6ecg9b3nyvfpws4af</v>
+      </c>
+      <c r="R19" t="str" xml:space="preserve">
+        <v xml:space="preserve">Agent: Namaste! I am calling on behalf of Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
+Prospect: Gujarati.
+Agent: ખૂબ સારું! હું ગુજરાતીમાં વાત કરીશ।વિશ્વ ઉમિયા ફાઉન્ડેશન આધ્યાત્મ, શિક્ષણ, આરોગ્ય અને સમાજ સેવા દ્વારા સમાજની સેવા કરે છે.અમારા મિશનનું કેન્દ્ર છે ઉમિયા ધામ — જે વિશ્વના સૌથી ઊંચા મંદિરોમાંથી એક તરીકે વિકસાવવામાં આવી રહ્યું છે, જે શ્રદ્ધા, એકતા અને ભક્તિનું પ્રતીક છે.શું તમે વધુ જાણવા, અમારી વેબસાઇટ જોવા, અથવા અમારી ટીમ સાથે જોડાવા ઇચ્છો છો?
+Prospect: હા, હું તમારી team સાથે જોડાવા ઇચ્છું છું.
+Agent: ખૂબ સારું! હું તમને અભી અમારી ટીમ સાથે જોડું છું. કૃપા કરીને લાઇન પર રહો.</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2026-04-28T10:33:40.534Z</v>
+      </c>
+      <c r="C20" t="str">
+        <v>+0170247</v>
+      </c>
+      <c r="D20" t="str">
+        <v/>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20" t="str">
+        <v>English</v>
+      </c>
+      <c r="J20" t="str">
+        <v>en</v>
+      </c>
+      <c r="K20" t="str">
+        <v>English</v>
+      </c>
+      <c r="L20" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M20" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="N20" t="str">
+        <v>unknown</v>
+      </c>
+      <c r="O20" t="str">
+        <v>Agent: Namaste! I am calling on behalf of Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?</v>
+      </c>
+      <c r="P20" t="str">
+        <v/>
+      </c>
+      <c r="Q20" t="str">
+        <v>conv_3601kq9tcdw9f3fv7qkda9n6qfyx</v>
+      </c>
+      <c r="R20" t="str">
+        <v>Agent: Namaste! I am calling on behalf of Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="str">
+        <v>2026-04-28T10:32:58.922Z</v>
+      </c>
+      <c r="C21" t="str">
+        <v>+0170247</v>
+      </c>
+      <c r="D21" t="str">
+        <v/>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21" t="str">
+        <v>English</v>
+      </c>
+      <c r="J21" t="str">
+        <v>en</v>
+      </c>
+      <c r="K21" t="str">
+        <v>English</v>
+      </c>
+      <c r="L21" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M21" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="N21" t="str">
+        <v>unknown</v>
+      </c>
+      <c r="O21" t="str">
+        <v>Agent: Namaste! I am calling on behalf of Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?</v>
+      </c>
+      <c r="P21" t="str">
+        <v/>
+      </c>
+      <c r="Q21" t="str">
+        <v>conv_3501kq9tbm41eytsj0chf094p939</v>
+      </c>
+      <c r="R21" t="str">
+        <v>Agent: Namaste! I am calling on behalf of Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?</v>
+      </c>
+    </row>
+    <row r="22" xml:space="preserve">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="str">
+        <v>2026-04-28T10:21:35.012Z</v>
+      </c>
+      <c r="C22" t="str">
+        <v>+0170247</v>
+      </c>
+      <c r="D22" t="str">
+        <v/>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22">
+        <v>13</v>
+      </c>
+      <c r="I22" t="str">
+        <v>Gujarati</v>
+      </c>
+      <c r="J22" t="str">
+        <v>gu</v>
+      </c>
+      <c r="K22" t="str">
+        <v>English, Gujarati</v>
+      </c>
+      <c r="L22" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M22" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="N22" t="str">
+        <v>unknown</v>
+      </c>
+      <c r="O22" t="str">
+        <v>માં આટલી કરીએ તમારી ધાન્ય વાંચીએ છીએ તો તમારી ધાન્ય વાંચીએ છીએ તો તમારી ધાન્ય વાંચીએ છીએ તો તમારી ધાન્ય વાંચીએ છીએ તોતમારી ધાન્ય વાંચીએ છીએ તો તમ�</v>
+      </c>
+      <c r="P22" t="str">
+        <v/>
+      </c>
+      <c r="Q22" t="str">
+        <v>conv_3901kq9sk35rebya3f068cvk3jz4</v>
+      </c>
+      <c r="R22" t="str" xml:space="preserve">
+        <v xml:space="preserve">Agent: Namaste 
+I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
+Would you be willing to hear a brief message about Maa Umiya and our mission?
+Umiya Dham is being developed as one of the tallest temples in the world, symbolizing strength, devotion, and cultural pride, and spreading a message of unity and spirituality.
+At Vishv Umiya Foundation, the mission is to uplift society through spirituality, education, healthcare, and community service, creating a be...
+Prospect: ગુજરાતી.
+Agent: સ્વાગત છે મિત્ર.કૃપા કરીને જણાવો કે તમે કયા ભાષામાં વાત કરવામાં આરામદાયક માનો છો — ગુજરાતી, હિન્દી કે અંગ્રેજી?
+Prospect: થેંક્યુ ભાઈ.
+Agent: તમારો આભાર, મિત્ર. [સ્નેહપૂર્વક]હવે કૃપા કરીને જણાવો કે તમે કયા ભાષામાં વાત કરવામાં આરામદાયક માનો છો — ગુજરાતી, હિન્દી કે અંગ્રેજી?
+Prospect: ગુજરાતી.ગુજરાતી.
+Agent: ...
+Prospect: હા, હા. પણ પાછું વિચારું છું.
+Agent: સમજી ગયો મિત્ર. [શાંત] કૃપા કરીને કહો કે હવે તમે કયા ભાષામાં વાત કરવા માંગો છો — ગુજરાતી, હિન્દી કે અંગ્રેજી? હું તમારી સાથે તમારી આરામદાયક ભાષામાં જ વાત કરીશ...
+Prospect: કુચરાટી.કુચરાટી.
+Agent: ...
+Prospect: માં આટલી કરીએ તમારી ધાન્ય વાંચીએ છીએ તો તમારી ધાન્ય વાંચીએ છીએ તો તમારી ધાન્ય વાંચીએ છીએ તો તમારી ધાન્ય વાંચીએ છીએ તોતમારી ધાન્ય વાંચીએ છીએ તો તમ�
+Agent: મિત્ર, માફ કરશો, હું થોડો અસ્પષ્ટ સંદેશ સમજી શક્યો નથી. કૃપા કરીને ફરીથી સ્પષ્ટ રીતે કહો કે તમે કયા ભાષામાં વાત કરવા માંગો છો — ગુજરાતી, હિન્દી કે અંગ્રેજી? હું તમારી સાથે તમારી આરામદાયક ભાષામાં જ વાત કરીશ...</v>
+      </c>
+    </row>
+    <row r="23" xml:space="preserve">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="str">
+        <v>2026-04-28T10:19:01.663Z</v>
+      </c>
+      <c r="C23" t="str">
+        <v>+0170247</v>
+      </c>
+      <c r="D23" t="str">
+        <v/>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23">
+        <v>13</v>
+      </c>
+      <c r="I23" t="str">
+        <v>Gujarati</v>
+      </c>
+      <c r="J23" t="str">
+        <v>gu</v>
+      </c>
+      <c r="K23" t="str">
+        <v>English, Gujarati, Hindi</v>
+      </c>
+      <c r="L23" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M23" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="N23" t="str">
+        <v>unknown</v>
+      </c>
+      <c r="O23" t="str">
+        <v>બીજું?બીજું?</v>
+      </c>
+      <c r="P23" t="str">
+        <v/>
+      </c>
+      <c r="Q23" t="str">
+        <v>conv_3701kq9sereze8vb2wbfa8arb7qp</v>
+      </c>
+      <c r="R23" t="str" xml:space="preserve">
+        <v xml:space="preserve">Agent: Namaste 
+I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
+Would you be willing to hear a brief message about Maa Umiya and our mission?
+Umiya Dham is being developed as one of the tallest temples in the world, symbolizing strength, devotion, and cultural pride, and spreading...
+Prospect: Gujarat.ગુજરાત.
+Agent: સ્વાગત છે મિત્ર.કૃપા કરીને જણાવો કે તમે કયા ભાષામાં વાત કરવામાં આરામદાયક માનો છો — ગુજરાતી, હિન્દી કે અંગ્રેજી?
+Prospect: હિન્દી.
+Agent: स्वागत है मित्र। कृपया बताएं कि आप किस भाषा में बातचीत करने में सहज महसूस करते हैं — हिंदी, गुजराती या अंग्रेजी?
+Prospect: गुजराती।
+Agent: સ્વાગત છે મિત્ર. કૃપા કરીને જણાવો કે તમે કયા ભાષામાં વાત કરવામાં આરામદાયક માનો છો — ગુજરાતી, હિન્દી કે અંગ્રેજી?
+Prospect: ...
+Agent: કૃપા કરીને જણાવો કે તમે કયા ભાષામાં વાત કરવામાં આરામદાયક માનો છો — ગુજરાતી, હિન્દી કે અંગ્રેજી?[slow] હું તમારી સાથે તમારી પસંદગી મુજબ વાત કરીશ...
+Prospect: ગુજરાતી.
+Agent: સ્વાગત છે મિત્ર...
+Prospect: બીજું?બીજું?
+Agent: કૃપા કરીને જણાવો કે તમે કયા ભાષામાં વાત કરવામાં આરામદાયક માનો છો — ગુજરાતી, હિન્દી કે અંગ્રેજી?[slow] હું તમારી સાથે તમારી પસંદગી મુજબ વાત કરીશ...</v>
+      </c>
+    </row>
+    <row r="24" xml:space="preserve">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="str">
+        <v>2026-04-28T10:09:01.826Z</v>
+      </c>
+      <c r="C24" t="str">
+        <v/>
+      </c>
+      <c r="D24" t="str">
+        <v/>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24">
+        <v>9</v>
+      </c>
+      <c r="I24" t="str">
+        <v>Gujarati</v>
+      </c>
+      <c r="J24" t="str">
+        <v>gu</v>
+      </c>
+      <c r="K24" t="str">
+        <v>English, Gujarati</v>
+      </c>
+      <c r="L24" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M24" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="N24" t="str">
+        <v>unknown</v>
+      </c>
+      <c r="O24" t="str">
         <v>ના.</v>
       </c>
-      <c r="P2" t="str">
-        <v/>
-      </c>
-      <c r="Q2" t="str">
+      <c r="P24" t="str">
+        <v/>
+      </c>
+      <c r="Q24" t="str">
         <v>conv_9101kq9rx3nbf3hsqrspc9b7zk5q</v>
       </c>
-      <c r="R2" t="str" xml:space="preserve">
+      <c r="R24" t="str" xml:space="preserve">
         <v xml:space="preserve">Agent: Namaste 
 I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
 Would you be...
@@ -521,59 +1934,59 @@
 Agent: ...</v>
       </c>
     </row>
-    <row r="3" xml:space="preserve">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="str">
+    <row r="25" xml:space="preserve">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="str">
         <v>2026-04-28T10:06:59.684Z</v>
       </c>
-      <c r="C3" t="str">
-        <v/>
-      </c>
-      <c r="D3" t="str">
-        <v/>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
+      <c r="C25" t="str">
+        <v/>
+      </c>
+      <c r="D25" t="str">
+        <v/>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+      <c r="H25">
         <v>5</v>
       </c>
-      <c r="I3" t="str">
+      <c r="I25" t="str">
         <v>Hindi</v>
       </c>
-      <c r="J3" t="str">
+      <c r="J25" t="str">
         <v>hi</v>
       </c>
-      <c r="K3" t="str">
+      <c r="K25" t="str">
         <v>English, Hindi</v>
       </c>
-      <c r="L3" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="M3" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="N3" t="str">
+      <c r="L25" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M25" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="N25" t="str">
         <v>unknown</v>
       </c>
-      <c r="O3" t="str">
+      <c r="O25" t="str">
         <v>हाँ, मैं अधिक जानना चाहूंगा।</v>
       </c>
-      <c r="P3" t="str">
-        <v/>
-      </c>
-      <c r="Q3" t="str">
+      <c r="P25" t="str">
+        <v/>
+      </c>
+      <c r="Q25" t="str">
         <v>conv_7601kq9rv4d2e9rrjrjwdbm3b48p</v>
       </c>
-      <c r="R3" t="str" xml:space="preserve">
+      <c r="R25" t="str" xml:space="preserve">
         <v xml:space="preserve">Agent: Namaste 
 I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
 Would you be willing to hear a brief messa...
@@ -583,59 +1996,59 @@
 Agent: [excited] बहुत अच्छा! आप वेबसाइट पर अधिक जानकारी प्राप्त कर सकते हैं: https://www.vuf.org/क्या आप अपने...</v>
       </c>
     </row>
-    <row r="4" xml:space="preserve">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="str">
+    <row r="26" xml:space="preserve">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="str">
         <v>2026-04-28T10:01:48.637Z</v>
       </c>
-      <c r="C4" t="str">
-        <v/>
-      </c>
-      <c r="D4" t="str">
-        <v/>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4">
+      <c r="C26" t="str">
+        <v/>
+      </c>
+      <c r="D26" t="str">
+        <v/>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
+        <v/>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26">
         <v>7</v>
       </c>
-      <c r="I4" t="str">
+      <c r="I26" t="str">
         <v>Gujarati</v>
       </c>
-      <c r="J4" t="str">
+      <c r="J26" t="str">
         <v>gu</v>
       </c>
-      <c r="K4" t="str">
+      <c r="K26" t="str">
         <v>English, Gujarati</v>
       </c>
-      <c r="L4" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="M4" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="N4" t="str">
+      <c r="L26" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M26" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="N26" t="str">
         <v>unknown</v>
       </c>
-      <c r="O4" t="str">
+      <c r="O26" t="str">
         <v>હા।</v>
       </c>
-      <c r="P4" t="str">
-        <v/>
-      </c>
-      <c r="Q4" t="str">
+      <c r="P26" t="str">
+        <v/>
+      </c>
+      <c r="Q26" t="str">
         <v>conv_5701kq9rh34nfy9s02fpz6mb9cng</v>
       </c>
-      <c r="R4" t="str" xml:space="preserve">
+      <c r="R26" t="str" xml:space="preserve">
         <v xml:space="preserve">Agent: Namaste 
 I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
 Would you be willing to hear a ...
@@ -647,59 +2060,59 @@
 Agent: ધન્યવાદ. ઉમિયા ધામ વિશ્વના સૌથી ઊંચા મંદિરોમાંના એક તરીકે વિકસાવવામાં આવી રહ્યું છે, જે ભક્તિ, એકતા અને આધ્યાત્મિકતાનું પ્રતીક છે.વિશ્વ ઉમિયા ફાઉન્ડેશન આધ્યાત્મિકતા, શિક્ષણ, સ્વાસ્થ્ય અને સમાજની ઉન્નતિ દ્વારા સમાજની સેવા કરે છે.કેમ કે તમને વધુ જાણવા માંગો છો કે અમારી ટીમ સાથે જોડાવા માંગો છો?</v>
       </c>
     </row>
-    <row r="5" xml:space="preserve">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="str">
+    <row r="27" xml:space="preserve">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="str">
         <v>2026-04-28T09:49:46.217Z</v>
       </c>
-      <c r="C5" t="str">
-        <v/>
-      </c>
-      <c r="D5" t="str">
-        <v/>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
+      <c r="C27" t="str">
+        <v/>
+      </c>
+      <c r="D27" t="str">
+        <v/>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
+        <v/>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="H27">
         <v>5</v>
       </c>
-      <c r="I5" t="str">
+      <c r="I27" t="str">
         <v>Gujarati</v>
       </c>
-      <c r="J5" t="str">
+      <c r="J27" t="str">
         <v>gu</v>
       </c>
-      <c r="K5" t="str">
+      <c r="K27" t="str">
         <v>English, Gujarati</v>
       </c>
-      <c r="L5" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="M5" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="N5" t="str">
+      <c r="L27" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M27" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="N27" t="str">
         <v>unknown</v>
       </c>
-      <c r="O5" t="str">
+      <c r="O27" t="str">
         <v>...</v>
       </c>
-      <c r="P5" t="str">
-        <v/>
-      </c>
-      <c r="Q5" t="str">
+      <c r="P27" t="str">
+        <v/>
+      </c>
+      <c r="Q27" t="str">
         <v>conv_2601kq9qvs1jebds4t54m74mvpkt</v>
       </c>
-      <c r="R5" t="str" xml:space="preserve">
+      <c r="R27" t="str" xml:space="preserve">
         <v xml:space="preserve">Agent: Namaste 
 I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
 Would you be willing to hear...
@@ -709,62 +2122,62 @@
 Agent: કૃપા કરીને જણાવો, કે કેટલો સમય તમને લાગે છે?[slow] મેં તમને માતા ઉમિયા અને વિશ્વ ઉમિયા ફાઉન્ડેશન વિશે થોડી માહિતી આપવા માંગુ છું।...</v>
       </c>
     </row>
-    <row r="6" xml:space="preserve">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="str">
+    <row r="28" xml:space="preserve">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="str">
         <v>2026-04-28T09:43:59.661Z</v>
       </c>
-      <c r="C6" t="str">
-        <v/>
-      </c>
-      <c r="D6" t="str">
-        <v/>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6" t="str">
+      <c r="C28" t="str">
+        <v/>
+      </c>
+      <c r="D28" t="str">
+        <v/>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
+        <v/>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+      <c r="H28">
+        <v>1</v>
+      </c>
+      <c r="I28" t="str">
         <v>English</v>
       </c>
-      <c r="J6" t="str">
+      <c r="J28" t="str">
         <v>en</v>
       </c>
-      <c r="K6" t="str">
+      <c r="K28" t="str">
         <v>English</v>
       </c>
-      <c r="L6" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="M6" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="N6" t="str">
+      <c r="L28" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M28" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="N28" t="str">
         <v>unknown</v>
       </c>
-      <c r="O6" t="str" xml:space="preserve">
+      <c r="O28" t="str" xml:space="preserve">
         <v xml:space="preserve">Agent: Namaste 
 I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
 Would you be willing to hear a brief message about Maa Umiya and our mission?
 Umiya Dham is being develope</v>
       </c>
-      <c r="P6" t="str">
-        <v/>
-      </c>
-      <c r="Q6" t="str">
+      <c r="P28" t="str">
+        <v/>
+      </c>
+      <c r="Q28" t="str">
         <v>conv_3701kq9qgpj7fx5vbjnb0k742b1d</v>
       </c>
-      <c r="R6" t="str" xml:space="preserve">
+      <c r="R28" t="str" xml:space="preserve">
         <v xml:space="preserve">Agent: Namaste 
 I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
 Would you be willing to hear a brief message about Maa Umiya and our mission?
@@ -773,59 +2186,59 @@
 "Thank you for connecting with Vishv Umiya Foundation. We truly value your time. May Maa Umiya bless you and your family. Have a wonderful day...</v>
       </c>
     </row>
-    <row r="7" xml:space="preserve">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="str">
+    <row r="29" xml:space="preserve">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="str">
         <v>2026-04-28T09:43:34.372Z</v>
       </c>
-      <c r="C7" t="str">
-        <v/>
-      </c>
-      <c r="D7" t="str">
-        <v/>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7">
+      <c r="C29" t="str">
+        <v/>
+      </c>
+      <c r="D29" t="str">
+        <v/>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
+        <v/>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+      <c r="H29">
         <v>5</v>
       </c>
-      <c r="I7" t="str">
+      <c r="I29" t="str">
         <v>Gujarati</v>
       </c>
-      <c r="J7" t="str">
+      <c r="J29" t="str">
         <v>gu</v>
       </c>
-      <c r="K7" t="str">
+      <c r="K29" t="str">
         <v>English, Gujarati</v>
       </c>
-      <c r="L7" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="M7" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="N7" t="str">
+      <c r="L29" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M29" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="N29" t="str">
         <v>unknown</v>
       </c>
-      <c r="O7" t="str">
+      <c r="O29" t="str">
         <v>...</v>
       </c>
-      <c r="P7" t="str">
-        <v/>
-      </c>
-      <c r="Q7" t="str">
+      <c r="P29" t="str">
+        <v/>
+      </c>
+      <c r="Q29" t="str">
         <v>conv_3201kq9qgyvae3sby1cd2k9d91wx</v>
       </c>
-      <c r="R7" t="str" xml:space="preserve">
+      <c r="R29" t="str" xml:space="preserve">
         <v xml:space="preserve">Agent: Namaste 
 I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
 Would you be willing to hear a brief message about Maa Umiya and our mission?
@@ -836,59 +2249,59 @@
 Agent: [soft] હું સમજું...</v>
       </c>
     </row>
-    <row r="8" xml:space="preserve">
-      <c r="A8">
+    <row r="30" xml:space="preserve">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="str">
+        <v>2026-04-28T09:41:51.754Z</v>
+      </c>
+      <c r="C30" t="str">
+        <v/>
+      </c>
+      <c r="D30" t="str">
+        <v/>
+      </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
+      <c r="F30" t="str">
+        <v/>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+      <c r="H30">
         <v>7</v>
       </c>
-      <c r="B8" t="str">
-        <v>2026-04-28T09:41:51.754Z</v>
-      </c>
-      <c r="C8" t="str">
-        <v/>
-      </c>
-      <c r="D8" t="str">
-        <v/>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-      <c r="H8">
-        <v>7</v>
-      </c>
-      <c r="I8" t="str">
+      <c r="I30" t="str">
         <v>English</v>
       </c>
-      <c r="J8" t="str">
+      <c r="J30" t="str">
         <v>en</v>
       </c>
-      <c r="K8" t="str">
+      <c r="K30" t="str">
         <v>English, Gujarati</v>
       </c>
-      <c r="L8" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="M8" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="N8" t="str">
+      <c r="L30" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M30" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="N30" t="str">
         <v>unknown</v>
       </c>
-      <c r="O8" t="str">
+      <c r="O30" t="str">
         <v>Thank you.</v>
       </c>
-      <c r="P8" t="str">
-        <v/>
-      </c>
-      <c r="Q8" t="str">
+      <c r="P30" t="str">
+        <v/>
+      </c>
+      <c r="Q30" t="str">
         <v>conv_9401kq9qd86qea2rg6xtnzj9fw5s</v>
       </c>
-      <c r="R8" t="str" xml:space="preserve">
+      <c r="R30" t="str" xml:space="preserve">
         <v xml:space="preserve">Agent: Namaste 
 I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
 Would you be willing ...
@@ -900,59 +2313,59 @@
 Agent: You're welcome. May Maa Umiya bless you and your family. Have a wonderful da...</v>
       </c>
     </row>
-    <row r="9" xml:space="preserve">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="str">
+    <row r="31" xml:space="preserve">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="str">
         <v>2026-04-28T09:40:49.805Z</v>
       </c>
-      <c r="C9" t="str">
-        <v/>
-      </c>
-      <c r="D9" t="str">
-        <v/>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-      <c r="H9">
+      <c r="C31" t="str">
+        <v/>
+      </c>
+      <c r="D31" t="str">
+        <v/>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31" t="str">
+        <v/>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+      <c r="H31">
         <v>3</v>
       </c>
-      <c r="I9" t="str">
+      <c r="I31" t="str">
         <v>English</v>
       </c>
-      <c r="J9" t="str">
+      <c r="J31" t="str">
         <v>en</v>
       </c>
-      <c r="K9" t="str">
+      <c r="K31" t="str">
         <v>English</v>
       </c>
-      <c r="L9" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="M9" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="N9" t="str">
+      <c r="L31" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M31" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="N31" t="str">
         <v>unknown</v>
       </c>
-      <c r="O9" t="str">
+      <c r="O31" t="str">
         <v>Hello?</v>
       </c>
-      <c r="P9" t="str">
-        <v/>
-      </c>
-      <c r="Q9" t="str">
+      <c r="P31" t="str">
+        <v/>
+      </c>
+      <c r="Q31" t="str">
         <v>conv_3701kq9qc50jf66b0kyccx2f2687</v>
       </c>
-      <c r="R9" t="str" xml:space="preserve">
+      <c r="R31" t="str" xml:space="preserve">
         <v xml:space="preserve">Agent: Namaste 
 I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
 Would you be willing to hear a brief message about Maa Umiya and our mission?
@@ -961,59 +2374,59 @@
 Agent: Hello, I'm here.Would you be willing to hear a brief message about Maa Umiya and Vishv Umiya Foundation?</v>
       </c>
     </row>
-    <row r="10" xml:space="preserve">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="str">
+    <row r="32" xml:space="preserve">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="str">
         <v>2026-04-28T09:40:25.307Z</v>
       </c>
-      <c r="C10" t="str">
-        <v/>
-      </c>
-      <c r="D10" t="str">
-        <v/>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-      <c r="H10">
+      <c r="C32" t="str">
+        <v/>
+      </c>
+      <c r="D32" t="str">
+        <v/>
+      </c>
+      <c r="E32" t="str">
+        <v/>
+      </c>
+      <c r="F32" t="str">
+        <v/>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+      <c r="H32">
         <v>11</v>
       </c>
-      <c r="I10" t="str">
+      <c r="I32" t="str">
         <v>English</v>
       </c>
-      <c r="J10" t="str">
+      <c r="J32" t="str">
         <v>en</v>
       </c>
-      <c r="K10" t="str">
+      <c r="K32" t="str">
         <v>English, Hindi, Gujarati</v>
       </c>
-      <c r="L10" t="str">
+      <c r="L32" t="str">
         <v>Yes</v>
       </c>
-      <c r="M10" t="str">
+      <c r="M32" t="str">
         <v>Willing to join</v>
       </c>
-      <c r="N10" t="str">
+      <c r="N32" t="str">
         <v>willing_to_join</v>
       </c>
-      <c r="O10" t="str">
+      <c r="O32" t="str">
         <v>Yes.</v>
       </c>
-      <c r="P10" t="str">
-        <v/>
-      </c>
-      <c r="Q10" t="str">
+      <c r="P32" t="str">
+        <v/>
+      </c>
+      <c r="Q32" t="str">
         <v>conv_9701kq9q8j4yftes3c09h4h0z6hs</v>
       </c>
-      <c r="R10" t="str" xml:space="preserve">
+      <c r="R32" t="str" xml:space="preserve">
         <v xml:space="preserve">Agent: Namaste 
 I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
 Would you be willing to hear a brief message about Maa Umiya and our mission?
@@ -1032,59 +2445,59 @@
 Agent: [pleasant] Wonderful I’ll connect you with our team right away. Thank you for your time and interest in Vishv Umiya Foundation. May Maa Umiya bless you and your family. Have a wonderful day. Jai Maa Umiya 🙏</v>
       </c>
     </row>
-    <row r="11" xml:space="preserve">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="str">
+    <row r="33" xml:space="preserve">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="str">
         <v>2026-04-28T08:12:20.478Z</v>
       </c>
-      <c r="C11" t="str">
+      <c r="C33" t="str">
         <v>+919328481970</v>
       </c>
-      <c r="D11" t="str">
-        <v/>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-      <c r="H11">
+      <c r="D33" t="str">
+        <v/>
+      </c>
+      <c r="E33" t="str">
+        <v/>
+      </c>
+      <c r="F33" t="str">
+        <v/>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+      <c r="H33">
         <v>7</v>
       </c>
-      <c r="I11" t="str">
+      <c r="I33" t="str">
         <v>Gujarati</v>
       </c>
-      <c r="J11" t="str">
+      <c r="J33" t="str">
         <v>gu</v>
       </c>
-      <c r="K11" t="str">
+      <c r="K33" t="str">
         <v>English, Gujarati</v>
       </c>
-      <c r="L11" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="M11" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="N11" t="str">
+      <c r="L33" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M33" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="N33" t="str">
         <v>unknown</v>
       </c>
-      <c r="O11" t="str">
+      <c r="O33" t="str">
         <v>હા, મારે વધારે જાણવું છે વિશ્વ ઓમિયા foundation ના વિશે.</v>
       </c>
-      <c r="P11" t="str">
+      <c r="P33" t="str">
         <v>CA73824daf7f18e54de49c0bfa20f48f46</v>
       </c>
-      <c r="Q11" t="str">
+      <c r="Q33" t="str">
         <v>conv_6801kq9j82gce5087xcrta8mq6y4</v>
       </c>
-      <c r="R11" t="str" xml:space="preserve">
+      <c r="R33" t="str" xml:space="preserve">
         <v xml:space="preserve">Agent: Namaste 
 I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
 Would you be willing to hear a brief message about Maa Umiya a...
@@ -1096,59 +2509,59 @@
 Agent: [calm] આભાર, તમારો રસ માટે ખુબ ખુબ આભાર. વિશ્વ ઉમિયા ફાઉન્ડેશન અમદાવાદમાં આધ્યાત્મિકતા, શિક્ષણ, સ્વાસ્થ્ય અને સમુદાય ઉન્નતિ માટ...</v>
       </c>
     </row>
-    <row r="12" xml:space="preserve">
-      <c r="A12">
+    <row r="34" xml:space="preserve">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="str">
+        <v>2026-04-28T08:09:58.868Z</v>
+      </c>
+      <c r="C34" t="str">
+        <v/>
+      </c>
+      <c r="D34" t="str">
+        <v/>
+      </c>
+      <c r="E34" t="str">
+        <v/>
+      </c>
+      <c r="F34" t="str">
+        <v/>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+      <c r="H34">
         <v>11</v>
       </c>
-      <c r="B12" t="str">
-        <v>2026-04-28T08:09:58.868Z</v>
-      </c>
-      <c r="C12" t="str">
-        <v/>
-      </c>
-      <c r="D12" t="str">
-        <v/>
-      </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-      <c r="H12">
-        <v>11</v>
-      </c>
-      <c r="I12" t="str">
+      <c r="I34" t="str">
         <v>Gujarati</v>
       </c>
-      <c r="J12" t="str">
+      <c r="J34" t="str">
         <v>gu</v>
       </c>
-      <c r="K12" t="str">
+      <c r="K34" t="str">
         <v>English, Gujarati</v>
       </c>
-      <c r="L12" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="M12" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="N12" t="str">
+      <c r="L34" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M34" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="N34" t="str">
         <v>unknown</v>
       </c>
-      <c r="O12" t="str">
+      <c r="O34" t="str">
         <v>જય મા ઉમિયા.</v>
       </c>
-      <c r="P12" t="str">
-        <v/>
-      </c>
-      <c r="Q12" t="str">
+      <c r="P34" t="str">
+        <v/>
+      </c>
+      <c r="Q34" t="str">
         <v>conv_5801kq9j2ptef53sdz089y7qarx1</v>
       </c>
-      <c r="R12" t="str" xml:space="preserve">
+      <c r="R34" t="str" xml:space="preserve">
         <v xml:space="preserve">Agent: Namaste 
 I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
 Would you be willing to hear a brief message about Maa Umiya and our mission?
@@ -1166,59 +2579,59 @@
 Agent: જય મા ઉમિયા! મા ઉમિયા તમને અને તમારા પરિવારને સદા આશીર્વાદ આપે. શુભ દિવસ રહે...</v>
       </c>
     </row>
-    <row r="13" xml:space="preserve">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" t="str">
+    <row r="35" xml:space="preserve">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="str">
         <v>2026-04-28T08:08:49.302Z</v>
       </c>
-      <c r="C13" t="str">
-        <v/>
-      </c>
-      <c r="D13" t="str">
-        <v/>
-      </c>
-      <c r="E13" t="str">
-        <v/>
-      </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-      <c r="H13">
+      <c r="C35" t="str">
+        <v/>
+      </c>
+      <c r="D35" t="str">
+        <v/>
+      </c>
+      <c r="E35" t="str">
+        <v/>
+      </c>
+      <c r="F35" t="str">
+        <v/>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+      <c r="H35">
         <v>5</v>
       </c>
-      <c r="I13" t="str">
+      <c r="I35" t="str">
         <v>Gujarati</v>
       </c>
-      <c r="J13" t="str">
+      <c r="J35" t="str">
         <v>gu</v>
       </c>
-      <c r="K13" t="str">
+      <c r="K35" t="str">
         <v>English, Gujarati</v>
       </c>
-      <c r="L13" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="M13" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="N13" t="str">
+      <c r="L35" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M35" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="N35" t="str">
         <v>unknown</v>
       </c>
-      <c r="O13" t="str">
+      <c r="O35" t="str">
         <v>ગુજરાતી.</v>
       </c>
-      <c r="P13" t="str">
-        <v/>
-      </c>
-      <c r="Q13" t="str">
+      <c r="P35" t="str">
+        <v/>
+      </c>
+      <c r="Q35" t="str">
         <v>conv_0601kq9j10aff04bte8ak7gpqqbx</v>
       </c>
-      <c r="R13" t="str" xml:space="preserve">
+      <c r="R35" t="str" xml:space="preserve">
         <v xml:space="preserve">Agent: Namaste 
 I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
 Would you be willing to hear a brief message about Maa Umiya and our mission?
@@ -1231,59 +2644,59 @@
 Agent: ધન્યવાદ. મા ઉમિયા અને વિશ્વ ઉમિયા ફાઉન્ડેશન વિશે સંક્ષિપ્ત સમાચાર સાંભળવા તમારી સા...</v>
       </c>
     </row>
-    <row r="14" xml:space="preserve">
-      <c r="A14">
+    <row r="36" xml:space="preserve">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="str">
+        <v>2026-04-28T08:04:48.175Z</v>
+      </c>
+      <c r="C36" t="str">
+        <v/>
+      </c>
+      <c r="D36" t="str">
+        <v/>
+      </c>
+      <c r="E36" t="str">
+        <v/>
+      </c>
+      <c r="F36" t="str">
+        <v/>
+      </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
+      <c r="H36">
         <v>13</v>
       </c>
-      <c r="B14" t="str">
-        <v>2026-04-28T08:04:48.175Z</v>
-      </c>
-      <c r="C14" t="str">
-        <v/>
-      </c>
-      <c r="D14" t="str">
-        <v/>
-      </c>
-      <c r="E14" t="str">
-        <v/>
-      </c>
-      <c r="F14" t="str">
-        <v/>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-      <c r="H14">
-        <v>13</v>
-      </c>
-      <c r="I14" t="str">
+      <c r="I36" t="str">
         <v>Hindi</v>
       </c>
-      <c r="J14" t="str">
+      <c r="J36" t="str">
         <v>hi</v>
       </c>
-      <c r="K14" t="str">
+      <c r="K36" t="str">
         <v>English, Gujarati, Hindi</v>
       </c>
-      <c r="L14" t="str">
+      <c r="L36" t="str">
         <v>Yes</v>
       </c>
-      <c r="M14" t="str">
+      <c r="M36" t="str">
         <v>Willing to join</v>
       </c>
-      <c r="N14" t="str">
+      <c r="N36" t="str">
         <v>willing_to_join</v>
       </c>
-      <c r="O14" t="str">
+      <c r="O36" t="str">
         <v>Okay. हाँ, मैं वही हूँ।</v>
       </c>
-      <c r="P14" t="str">
-        <v/>
-      </c>
-      <c r="Q14" t="str">
+      <c r="P36" t="str">
+        <v/>
+      </c>
+      <c r="Q36" t="str">
         <v>conv_9201kq9hsbc8egfs31f788amy56w</v>
       </c>
-      <c r="R14" t="str" xml:space="preserve">
+      <c r="R36" t="str" xml:space="preserve">
         <v xml:space="preserve">Agent: Namaste 
 I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
 Would you be willing to hear a brief message about Maa Umiya and our mission?
@@ -1304,59 +2717,59 @@
 Agent: आपका स्वागत है।[grateful] माँ उमिया आपके और आपके परिवार के जीवन में शांति और सुख लाएं।[peaceful] आपका दिन शुभ हो।जय माँ उमिया 🙏</v>
       </c>
     </row>
-    <row r="15" xml:space="preserve">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15" t="str">
+    <row r="37" xml:space="preserve">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="str">
         <v>2026-04-28T08:02:30.875Z</v>
       </c>
-      <c r="C15" t="str">
-        <v/>
-      </c>
-      <c r="D15" t="str">
-        <v/>
-      </c>
-      <c r="E15" t="str">
-        <v/>
-      </c>
-      <c r="F15" t="str">
-        <v/>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-      <c r="H15">
+      <c r="C37" t="str">
+        <v/>
+      </c>
+      <c r="D37" t="str">
+        <v/>
+      </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
+      <c r="F37" t="str">
+        <v/>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+      <c r="H37">
         <v>9</v>
       </c>
-      <c r="I15" t="str">
+      <c r="I37" t="str">
         <v>English</v>
       </c>
-      <c r="J15" t="str">
+      <c r="J37" t="str">
         <v>en</v>
       </c>
-      <c r="K15" t="str">
+      <c r="K37" t="str">
         <v>English, Gujarati, Hindi</v>
       </c>
-      <c r="L15" t="str">
+      <c r="L37" t="str">
         <v>Yes</v>
       </c>
-      <c r="M15" t="str">
+      <c r="M37" t="str">
         <v>Willing to join</v>
       </c>
-      <c r="N15" t="str">
+      <c r="N37" t="str">
         <v>willing_to_join</v>
       </c>
-      <c r="O15" t="str">
+      <c r="O37" t="str">
         <v>Okay. Sir.</v>
       </c>
-      <c r="P15" t="str">
-        <v/>
-      </c>
-      <c r="Q15" t="str">
+      <c r="P37" t="str">
+        <v/>
+      </c>
+      <c r="Q37" t="str">
         <v>conv_5901kq9hptgbe6rt4tjjqhnfmwk3</v>
       </c>
-      <c r="R15" t="str" xml:space="preserve">
+      <c r="R37" t="str" xml:space="preserve">
         <v xml:space="preserve">Agent: Namaste 
 I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
 Would you be ...
@@ -1370,115 +2783,115 @@
 Agent: सारा, महोदय। क्या आप माँ उमिया और विश्व उमिया फाउंडेशन के बारे में एक संक्षिप्त संदेश सुनने के लिए तैयार हैं?</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" t="str">
+    <row r="38">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="str">
         <v>2026-04-28T06:42:54.419Z</v>
       </c>
-      <c r="C16" t="str">
-        <v/>
-      </c>
-      <c r="D16" t="str">
-        <v/>
-      </c>
-      <c r="E16" t="str">
-        <v/>
-      </c>
-      <c r="F16" t="str">
-        <v/>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-      <c r="H16">
-        <v>1</v>
-      </c>
-      <c r="I16" t="str">
+      <c r="C38" t="str">
+        <v/>
+      </c>
+      <c r="D38" t="str">
+        <v/>
+      </c>
+      <c r="E38" t="str">
+        <v/>
+      </c>
+      <c r="F38" t="str">
+        <v/>
+      </c>
+      <c r="G38">
+        <v>1</v>
+      </c>
+      <c r="H38">
+        <v>1</v>
+      </c>
+      <c r="I38" t="str">
         <v>English</v>
       </c>
-      <c r="J16" t="str">
+      <c r="J38" t="str">
         <v>en</v>
       </c>
-      <c r="K16" t="str">
+      <c r="K38" t="str">
         <v>English</v>
       </c>
-      <c r="L16" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="M16" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="N16" t="str">
+      <c r="L38" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M38" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="N38" t="str">
         <v>unknown</v>
       </c>
-      <c r="O16" t="str">
+      <c r="O38" t="str">
         <v>Transcript: Summary couldn't be generated for this call.</v>
       </c>
-      <c r="P16" t="str">
-        <v/>
-      </c>
-      <c r="Q16" t="str">
+      <c r="P38" t="str">
+        <v/>
+      </c>
+      <c r="Q38" t="str">
         <v>conv_7301kq9d735ve92stwtsszksq7v2</v>
       </c>
-      <c r="R16" t="str">
+      <c r="R38" t="str">
         <v>Transcript: Summary couldn't be generated for this call.</v>
       </c>
     </row>
-    <row r="17" xml:space="preserve">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17" t="str">
+    <row r="39" xml:space="preserve">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="str">
         <v>2026-04-28T06:42:53.484Z</v>
       </c>
-      <c r="C17" t="str">
-        <v/>
-      </c>
-      <c r="D17" t="str">
-        <v/>
-      </c>
-      <c r="E17" t="str">
-        <v/>
-      </c>
-      <c r="F17" t="str">
-        <v/>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-      <c r="H17">
+      <c r="C39" t="str">
+        <v/>
+      </c>
+      <c r="D39" t="str">
+        <v/>
+      </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
+      <c r="F39" t="str">
+        <v/>
+      </c>
+      <c r="G39">
+        <v>1</v>
+      </c>
+      <c r="H39">
         <v>9</v>
       </c>
-      <c r="I17" t="str">
+      <c r="I39" t="str">
         <v>Gujarati</v>
       </c>
-      <c r="J17" t="str">
+      <c r="J39" t="str">
         <v>gu</v>
       </c>
-      <c r="K17" t="str">
+      <c r="K39" t="str">
         <v>English, Gujarati</v>
       </c>
-      <c r="L17" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="M17" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="N17" t="str">
+      <c r="L39" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M39" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="N39" t="str">
         <v>unknown</v>
       </c>
-      <c r="O17" t="str">
+      <c r="O39" t="str">
         <v>હા</v>
       </c>
-      <c r="P17" t="str">
-        <v/>
-      </c>
-      <c r="Q17" t="str">
+      <c r="P39" t="str">
+        <v/>
+      </c>
+      <c r="Q39" t="str">
         <v>conv_9001kq9cx1bceky9cfvjzpq4tc09</v>
       </c>
-      <c r="R17" t="str" xml:space="preserve">
+      <c r="R39" t="str" xml:space="preserve">
         <v xml:space="preserve">Agent: Namaste 
 I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
 Would you be willing to hear a brief message about Maa Umiya and our mission?
@@ -1495,62 +2908,62 @@
 Agent: ધન્યવાદ 🙏યુમિયા ધામ વિશ્વના સૌથી ઊંચા મંદિરોમાંના એક તરીકે વિકસાવવામાં આવી રહ્યું છે, જે આસ્થા, એકતા અને ભક્તિનું પ્રતીક છે.વિશ્વ ઉમિયા ફાઉન્ડેશન આધ્યાત્મિકતા, શિક્ષણ, સ્વાસ્...</v>
       </c>
     </row>
-    <row r="18" xml:space="preserve">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18" t="str">
+    <row r="40" xml:space="preserve">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="str">
         <v>2026-04-28T06:31:37.032Z</v>
       </c>
-      <c r="C18" t="str">
-        <v/>
-      </c>
-      <c r="D18" t="str">
-        <v/>
-      </c>
-      <c r="E18" t="str">
-        <v/>
-      </c>
-      <c r="F18" t="str">
-        <v/>
-      </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-      <c r="H18">
-        <v>1</v>
-      </c>
-      <c r="I18" t="str">
+      <c r="C40" t="str">
+        <v/>
+      </c>
+      <c r="D40" t="str">
+        <v/>
+      </c>
+      <c r="E40" t="str">
+        <v/>
+      </c>
+      <c r="F40" t="str">
+        <v/>
+      </c>
+      <c r="G40">
+        <v>1</v>
+      </c>
+      <c r="H40">
+        <v>1</v>
+      </c>
+      <c r="I40" t="str">
         <v>English</v>
       </c>
-      <c r="J18" t="str">
+      <c r="J40" t="str">
         <v>en</v>
       </c>
-      <c r="K18" t="str">
+      <c r="K40" t="str">
         <v>English</v>
       </c>
-      <c r="L18" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="M18" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="N18" t="str">
+      <c r="L40" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M40" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="N40" t="str">
         <v>unknown</v>
       </c>
-      <c r="O18" t="str" xml:space="preserve">
+      <c r="O40" t="str" xml:space="preserve">
         <v xml:space="preserve">Agent: Namaste 
 I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
 Would you be willing to hear a brief message about Maa Umiya and our mission?
 Umiya Dham is being develope</v>
       </c>
-      <c r="P18" t="str">
-        <v/>
-      </c>
-      <c r="Q18" t="str">
+      <c r="P40" t="str">
+        <v/>
+      </c>
+      <c r="Q40" t="str">
         <v>conv_8301kq9chf18f59barx86mgyqn9a</v>
       </c>
-      <c r="R18" t="str" xml:space="preserve">
+      <c r="R40" t="str" xml:space="preserve">
         <v xml:space="preserve">Agent: Namaste 
 I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
 Would you be willing to hear a brief message about Maa Umiya and our mission?
@@ -1558,121 +2971,121 @@
 At Vishv Umiya Foundation, the mission is to uplift society through ...</v>
       </c>
     </row>
-    <row r="19" xml:space="preserve">
-      <c r="A19">
-        <v>18</v>
-      </c>
-      <c r="B19" t="str">
+    <row r="41" xml:space="preserve">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="str">
         <v>2026-04-28T06:30:38.685Z</v>
       </c>
-      <c r="C19" t="str">
-        <v/>
-      </c>
-      <c r="D19" t="str">
-        <v/>
-      </c>
-      <c r="E19" t="str">
-        <v/>
-      </c>
-      <c r="F19" t="str">
-        <v/>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-      <c r="H19">
-        <v>1</v>
-      </c>
-      <c r="I19" t="str">
+      <c r="C41" t="str">
+        <v/>
+      </c>
+      <c r="D41" t="str">
+        <v/>
+      </c>
+      <c r="E41" t="str">
+        <v/>
+      </c>
+      <c r="F41" t="str">
+        <v/>
+      </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
+      <c r="H41">
+        <v>1</v>
+      </c>
+      <c r="I41" t="str">
         <v>English</v>
       </c>
-      <c r="J19" t="str">
+      <c r="J41" t="str">
         <v>en</v>
       </c>
-      <c r="K19" t="str">
+      <c r="K41" t="str">
         <v>English</v>
       </c>
-      <c r="L19" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="M19" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="N19" t="str">
+      <c r="L41" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M41" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="N41" t="str">
         <v>unknown</v>
       </c>
-      <c r="O19" t="str" xml:space="preserve">
+      <c r="O41" t="str" xml:space="preserve">
         <v xml:space="preserve">Agent: Namaste 
 I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
 Would you be willing to hear a brief message about Maa Umiya and our mission?
 Umiya Dham is being develope</v>
       </c>
-      <c r="P19" t="str">
-        <v/>
-      </c>
-      <c r="Q19" t="str">
+      <c r="P41" t="str">
+        <v/>
+      </c>
+      <c r="Q41" t="str">
         <v>conv_6701kq9cg2eqer287bf4msmr1rhh</v>
       </c>
-      <c r="R19" t="str" xml:space="preserve">
+      <c r="R41" t="str" xml:space="preserve">
         <v xml:space="preserve">Agent: Namaste 
 I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
 Would you be willing to hear a brief message about Maa Umiya and our mission?
 Umiya Dham is being developed as one...</v>
       </c>
     </row>
-    <row r="20" xml:space="preserve">
-      <c r="A20">
+    <row r="42" xml:space="preserve">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="str">
+        <v>2026-04-28T05:38:40.915Z</v>
+      </c>
+      <c r="C42" t="str">
+        <v>+919328481970</v>
+      </c>
+      <c r="D42" t="str">
+        <v/>
+      </c>
+      <c r="E42" t="str">
+        <v/>
+      </c>
+      <c r="F42" t="str">
+        <v/>
+      </c>
+      <c r="G42">
+        <v>1</v>
+      </c>
+      <c r="H42">
         <v>19</v>
       </c>
-      <c r="B20" t="str">
-        <v>2026-04-28T05:38:40.915Z</v>
-      </c>
-      <c r="C20" t="str">
-        <v>+919328481970</v>
-      </c>
-      <c r="D20" t="str">
-        <v/>
-      </c>
-      <c r="E20" t="str">
-        <v/>
-      </c>
-      <c r="F20" t="str">
-        <v/>
-      </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
-      <c r="H20">
-        <v>19</v>
-      </c>
-      <c r="I20" t="str">
+      <c r="I42" t="str">
         <v>Hindi</v>
       </c>
-      <c r="J20" t="str">
+      <c r="J42" t="str">
         <v>hi</v>
       </c>
-      <c r="K20" t="str">
+      <c r="K42" t="str">
         <v>English, Hindi, Gujarati</v>
       </c>
-      <c r="L20" t="str">
+      <c r="L42" t="str">
         <v>Yes</v>
       </c>
-      <c r="M20" t="str">
+      <c r="M42" t="str">
         <v>Willing to join</v>
       </c>
-      <c r="N20" t="str">
+      <c r="N42" t="str">
         <v>willing_to_join</v>
       </c>
-      <c r="O20" t="str">
+      <c r="O42" t="str">
         <v>Okay, thank you.</v>
       </c>
-      <c r="P20" t="str">
+      <c r="P42" t="str">
         <v>CAd3fa254243c464a1730f45c7c56505ed</v>
       </c>
-      <c r="Q20" t="str">
+      <c r="Q42" t="str">
         <v>conv_5701kq99de98eg794mxra8d73bwb</v>
       </c>
-      <c r="R20" t="str" xml:space="preserve">
+      <c r="R42" t="str" xml:space="preserve">
         <v xml:space="preserve">Agent: Namaste 
 I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
 Would you be willing to hear a brief message about Maa Umiya and our mission?
@@ -1699,59 +3112,59 @@
 Agent: ...</v>
       </c>
     </row>
-    <row r="21" xml:space="preserve">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21" t="str">
+    <row r="43" xml:space="preserve">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="str">
         <v>2026-04-28T05:28:57.765Z</v>
       </c>
-      <c r="C21" t="str">
+      <c r="C43" t="str">
         <v>+919328481970</v>
       </c>
-      <c r="D21" t="str">
-        <v/>
-      </c>
-      <c r="E21" t="str">
-        <v/>
-      </c>
-      <c r="F21" t="str">
-        <v/>
-      </c>
-      <c r="G21">
-        <v>1</v>
-      </c>
-      <c r="H21">
+      <c r="D43" t="str">
+        <v/>
+      </c>
+      <c r="E43" t="str">
+        <v/>
+      </c>
+      <c r="F43" t="str">
+        <v/>
+      </c>
+      <c r="G43">
+        <v>1</v>
+      </c>
+      <c r="H43">
         <v>15</v>
       </c>
-      <c r="I21" t="str">
+      <c r="I43" t="str">
         <v>Hindi</v>
       </c>
-      <c r="J21" t="str">
+      <c r="J43" t="str">
         <v>hi</v>
       </c>
-      <c r="K21" t="str">
+      <c r="K43" t="str">
         <v>English, Hindi</v>
       </c>
-      <c r="L21" t="str">
+      <c r="L43" t="str">
         <v>Yes</v>
       </c>
-      <c r="M21" t="str">
+      <c r="M43" t="str">
         <v>Willing to join</v>
       </c>
-      <c r="N21" t="str">
+      <c r="N43" t="str">
         <v>willing_to_join</v>
       </c>
-      <c r="O21" t="str">
+      <c r="O43" t="str">
         <v>Yes, जानना चाहूँगा।</v>
       </c>
-      <c r="P21" t="str">
+      <c r="P43" t="str">
         <v>CA34c672f4a33b63610704a7d7f3ade6ab</v>
       </c>
-      <c r="Q21" t="str">
+      <c r="Q43" t="str">
         <v>conv_8201kq98we89eh6v5hpy42ncxkfd</v>
       </c>
-      <c r="R21" t="str" xml:space="preserve">
+      <c r="R43" t="str" xml:space="preserve">
         <v xml:space="preserve">Agent: Namaste 
 I am calling from Vishv Umiya Foundation. Which language are you comfortable speaking — English, Hindi, or Gujarati?
 Would you be willing to hear a brief message about Maa Umiya and our mission?
@@ -1775,7 +3188,7 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R43"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/call-qualifications.xlsx
+++ b/data/call-qualifications.xlsx
@@ -460,10 +460,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-28T11:20:10.827Z</v>
+        <v>2026-04-28T11:28:33.501Z</v>
       </c>
       <c r="C2" t="str">
-        <v>+919328481970</v>
+        <v>+917600795992</v>
       </c>
       <c r="D2" t="str">
         <v>completed</v>
@@ -478,7 +478,7 @@
         <v>1</v>
       </c>
       <c r="H2">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I2" t="str">
         <v>Gujarati</v>
@@ -490,38 +490,45 @@
         <v>English, Gujarati, Hindi</v>
       </c>
       <c r="L2" t="str">
-        <v>Yes</v>
+        <v>Unknown</v>
       </c>
       <c r="M2" t="str">
-        <v>Willing to join</v>
+        <v>Unknown</v>
       </c>
       <c r="N2" t="str">
-        <v>willing_to_join</v>
+        <v>unknown</v>
       </c>
       <c r="O2" t="str">
-        <v>Yeah, so my language, so my language is Gujarati.</v>
+        <v>नहीं।</v>
       </c>
       <c r="P2" t="str">
         <v>CAe8810eabc8222e0ec296ea49b31e2279</v>
       </c>
       <c r="Q2" t="str">
-        <v>conv_1601kq9x17zsfbmrr9c0fthc5f8a</v>
+        <v>conv_2301kq9xgrrvf989kxhwrqacc9bc</v>
       </c>
       <c r="R2" t="str" xml:space="preserve">
         <v xml:space="preserve">Agent: Namaste 🙏 Jai Maa Umiya I am calling from Vishv Umiya Foundation. 
-Before we...
-Prospect: કે બંધ કર દે તું.હા, બંધ કરી દે.બધી શબ્દ થઈ ગયું. આય ને, language choose કરો, પછી સમાધાન કરો. હું એને પૂછ્યું જ નહીં.હા.હા. હા. હા. હા
-Agent: [slow] કૃપા...
+Before we begin, which language are you most comfortable speaking — English, Hindi, or Gujarati?
+Prospect: Gujarati.
+Agent: ખૂબ સરસ, આપણે ગુજરાતીમાં વાત કરીશું. 🙏 [happy] શું આપ માઁ ઉમિયા અને વિશ્વ ઉમિયા ફાઉન્ડેશન વિશે થોડી વાત સાંભળવા તૈયાર છો?
+Prospect: જી.
+Agent: [happy] ઉમિયા ધામ વિશ્વના સૌથી ઊંચા મંદિરોમાંનું એક બની રહ્યું છે — જે માઁ ઉમિયા પ્રત્યેની શ્રદ્ધા, એકતા અને ભક્તિનું પ્રતીક છે. વિશ્વ ઉમિયા ફાઉન્ડેશન આધ્યાત્મિકતા, શિક્ષણ, આરોગ્ય સેવા અને સામાજિક ઉત્થાન દ્વારા સમાજની સેવા કરે છે. શું આપ વધુ જાણવા માંગો છો,...
+Prospect: હમ્મ, હમ્મ, હમ્મ.એ પણ સારું છે.એ પણ આય.હમ્મ, હમ્મ, હમ્મ. બરાબર. હમ્મ, હમ્મ, હમ્મ.હમ્મ, હમ્મ, હમ્મ.
+Agent: ...
+Prospect: નહીં, નહીં, જીપીએસસી.જીપીએસસી. જીપીએસસી.
+Agent: ...
+Prospect: ખૂબ સરસ.હા.
+Agent: શું આપ વધુ જાણવા માંગો છો, અથવા હું આપને અમારી ટીમ સાથે જોડું?
+Prospect: મને તો જાણવા માંગું છું.હમ્મ, તો તમે કેટલા વર્ષથી આ ક�
+Agent: તમે અમારી વેબસાઇટ www.vuf.org ની મુલાકાત લઈને સંપૂર્ણ વિગતો મેળવી શકો છો. વિશ્વ ઉમિયા ફાઉન્ડેશન સાથે જોડાવા બદલ આભાર. માઁ ઉમિયા આપને અને આપના પરિવારને આશીર્વાદ આપે. આપનો દિવસ શુભ રહે. જય માઁ ઉમિયા. 🙏
+Prospect: ધન્યવાદ.ધન્યવાદ.
+Agent: ...
+Prospect: નમસ્કાર.
 Prospect: Hindi.
-Agent: बहुत अच्छा, हम...
-Prospect: Yeah, so my language, so my language is Gujarati.
-Agent: [slow] ખૂબ સરસ, આપણે ગુજરાતીમાં વાત કરીશું. 🙏 [slow] શું આપ માઁ ઉમિયા અને વિશ્વ ઉમિયા ફાઉન્ડેશન...
-Prospect: હા.હમ્મ.
-Agent: ...
-Prospect: અને તમે કેવી રીતે કરો છો?તમે કેવી રીતે કરો છો?
-Agent: ...
-Prospect: બરાબર.બરાબર.
-Agent: [slow] ઉમિયા ધામ વિશ્વના સૌથી ઊંચા મંદિરોમાંનું એક બની રહ્યું છે — જે માઁ ઉ...</v>
+Agent: [happy] बहुत अच्छा, हम हिंदी में बात करेंगे। 🙏 क्या आप माँ उमिया और विश्व उमिया फाउंडेशन के बारे में एक छोटा सा संदेश सुनना चाहेंगे?
+Prospect: नहीं।
+Agent: विश्व उमिया फाउंडेशन से जुड़ने के लिए धन्यवाद। माँ उमिया आपको और आपके परिवार को आशीर्वाद दें। आपका दिन शुभ हो। जय म...</v>
       </c>
     </row>
     <row r="3" xml:space="preserve">
